--- a/UZClass/Hawkes.xlsx
+++ b/UZClass/Hawkes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marcoscscarreira/My Papers/UZModelUncertainty/UZClass/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1C1E9BA-A048-044C-BFD4-06EB5B8E2362}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1B3A91-DF2B-F34C-B3C5-4E0548E7E844}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29380" yWindow="460" windowWidth="26440" windowHeight="31920" activeTab="2" xr2:uid="{4FD1F5F7-7938-2F46-84BB-B96EA2FA67D0}"/>
+    <workbookView xWindow="-29380" yWindow="460" windowWidth="26440" windowHeight="31920" xr2:uid="{4FD1F5F7-7938-2F46-84BB-B96EA2FA67D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Simul" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="41">
   <si>
     <t>L_B</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>Calibrated Adjacency</t>
+  </si>
+  <si>
+    <t>Kernel Norms</t>
   </si>
 </sst>
 </file>
@@ -884,7 +887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1150,15 +1153,6 @@
     <xf numFmtId="169" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="79" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="79" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="79" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1169,6 +1163,17 @@
     <xf numFmtId="164" fontId="2" fillId="79" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="79" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="79" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2133,6 +2138,432 @@
             <a:t> Event</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1600" b="1"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="TextBox 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6015350D-3BA3-2E45-BCC0-7A8CE8F52AE9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="203200" y="24180800"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>q10</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>368300</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF03E070-90B2-CF47-B835-20F1AF73D723}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="241300" y="27482800"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>q30</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>153</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E9181D0-3075-1348-BB3E-20B4227C04E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="203200" y="30695900"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>q50</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>167</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>169</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3202EB69-1984-C34D-A110-49607BEFA104}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="215900" y="33959800"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>q70</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="TextBox 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D0F6D54-D801-0241-A058-589F382DB07A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="177800" y="37211000"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>q90</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B369519C-7B29-E74A-9B4B-668E3CCE11BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="228600" y="20878800"/>
+          <a:ext cx="1587500" cy="406400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1600" b="1"/>
+            <a:t>Mean</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -4474,23 +4905,23 @@
       <c r="C22" s="25">
         <v>38500</v>
       </c>
-      <c r="E22" s="215" t="s">
+      <c r="E22" s="227" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="216"/>
-      <c r="G22" s="216"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="216"/>
-      <c r="J22" s="216"/>
-      <c r="K22" s="216"/>
-      <c r="L22" s="216"/>
-      <c r="M22" s="216"/>
-      <c r="N22" s="216"/>
-      <c r="O22" s="216"/>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="216"/>
-      <c r="R22" s="216"/>
-      <c r="S22" s="217"/>
+      <c r="F22" s="228"/>
+      <c r="G22" s="228"/>
+      <c r="H22" s="228"/>
+      <c r="I22" s="228"/>
+      <c r="J22" s="228"/>
+      <c r="K22" s="228"/>
+      <c r="L22" s="228"/>
+      <c r="M22" s="228"/>
+      <c r="N22" s="228"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="228"/>
+      <c r="Q22" s="228"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="229"/>
       <c r="V22" s="54">
         <f>Y22/V3</f>
         <v>14.342552552552553</v>
@@ -5293,23 +5724,23 @@
       </c>
     </row>
     <row r="41" spans="2:26">
-      <c r="E41" s="215" t="s">
+      <c r="E41" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="216"/>
-      <c r="G41" s="216"/>
-      <c r="H41" s="216"/>
-      <c r="I41" s="216"/>
-      <c r="J41" s="216"/>
-      <c r="K41" s="216"/>
-      <c r="L41" s="216"/>
-      <c r="M41" s="216"/>
-      <c r="N41" s="216"/>
-      <c r="O41" s="216"/>
-      <c r="P41" s="216"/>
-      <c r="Q41" s="216"/>
-      <c r="R41" s="216"/>
-      <c r="S41" s="217"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="228"/>
+      <c r="Q41" s="228"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="229"/>
     </row>
     <row r="43" spans="2:26">
       <c r="E43" s="40" t="s">
@@ -6086,23 +6517,23 @@
       </c>
     </row>
     <row r="59" spans="5:26">
-      <c r="E59" s="215" t="s">
+      <c r="E59" s="227" t="s">
         <v>34</v>
       </c>
-      <c r="F59" s="216"/>
-      <c r="G59" s="216"/>
-      <c r="H59" s="216"/>
-      <c r="I59" s="216"/>
-      <c r="J59" s="216"/>
-      <c r="K59" s="216"/>
-      <c r="L59" s="216"/>
-      <c r="M59" s="216"/>
-      <c r="N59" s="216"/>
-      <c r="O59" s="216"/>
-      <c r="P59" s="216"/>
-      <c r="Q59" s="216"/>
-      <c r="R59" s="216"/>
-      <c r="S59" s="217"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="228"/>
+      <c r="H59" s="228"/>
+      <c r="I59" s="228"/>
+      <c r="J59" s="228"/>
+      <c r="K59" s="228"/>
+      <c r="L59" s="228"/>
+      <c r="M59" s="228"/>
+      <c r="N59" s="228"/>
+      <c r="O59" s="228"/>
+      <c r="P59" s="228"/>
+      <c r="Q59" s="228"/>
+      <c r="R59" s="228"/>
+      <c r="S59" s="229"/>
     </row>
     <row r="61" spans="5:26">
       <c r="E61" s="40" t="s">
@@ -6958,23 +7389,23 @@
       </c>
     </row>
     <row r="77" spans="5:25">
-      <c r="E77" s="215" t="s">
+      <c r="E77" s="227" t="s">
         <v>35</v>
       </c>
-      <c r="F77" s="216"/>
-      <c r="G77" s="216"/>
-      <c r="H77" s="216"/>
-      <c r="I77" s="216"/>
-      <c r="J77" s="216"/>
-      <c r="K77" s="216"/>
-      <c r="L77" s="216"/>
-      <c r="M77" s="216"/>
-      <c r="N77" s="216"/>
-      <c r="O77" s="216"/>
-      <c r="P77" s="216"/>
-      <c r="Q77" s="216"/>
-      <c r="R77" s="216"/>
-      <c r="S77" s="217"/>
+      <c r="F77" s="228"/>
+      <c r="G77" s="228"/>
+      <c r="H77" s="228"/>
+      <c r="I77" s="228"/>
+      <c r="J77" s="228"/>
+      <c r="K77" s="228"/>
+      <c r="L77" s="228"/>
+      <c r="M77" s="228"/>
+      <c r="N77" s="228"/>
+      <c r="O77" s="228"/>
+      <c r="P77" s="228"/>
+      <c r="Q77" s="228"/>
+      <c r="R77" s="228"/>
+      <c r="S77" s="229"/>
       <c r="V77" s="54">
         <f>Y77/V$3</f>
         <v>13.825195195195196</v>
@@ -7691,23 +8122,23 @@
       </c>
     </row>
     <row r="95" spans="5:19">
-      <c r="E95" s="215" t="s">
+      <c r="E95" s="227" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="216"/>
-      <c r="G95" s="216"/>
-      <c r="H95" s="216"/>
-      <c r="I95" s="216"/>
-      <c r="J95" s="216"/>
-      <c r="K95" s="216"/>
-      <c r="L95" s="216"/>
-      <c r="M95" s="216"/>
-      <c r="N95" s="216"/>
-      <c r="O95" s="216"/>
-      <c r="P95" s="216"/>
-      <c r="Q95" s="216"/>
-      <c r="R95" s="216"/>
-      <c r="S95" s="217"/>
+      <c r="F95" s="228"/>
+      <c r="G95" s="228"/>
+      <c r="H95" s="228"/>
+      <c r="I95" s="228"/>
+      <c r="J95" s="228"/>
+      <c r="K95" s="228"/>
+      <c r="L95" s="228"/>
+      <c r="M95" s="228"/>
+      <c r="N95" s="228"/>
+      <c r="O95" s="228"/>
+      <c r="P95" s="228"/>
+      <c r="Q95" s="228"/>
+      <c r="R95" s="228"/>
+      <c r="S95" s="229"/>
     </row>
     <row r="97" spans="5:19">
       <c r="E97" s="40" t="s">
@@ -8355,23 +8786,23 @@
       <c r="S111" s="19"/>
     </row>
     <row r="113" spans="5:19">
-      <c r="E113" s="215" t="s">
+      <c r="E113" s="227" t="s">
         <v>38</v>
       </c>
-      <c r="F113" s="216"/>
-      <c r="G113" s="216"/>
-      <c r="H113" s="216"/>
-      <c r="I113" s="216"/>
-      <c r="J113" s="216"/>
-      <c r="K113" s="216"/>
-      <c r="L113" s="216"/>
-      <c r="M113" s="216"/>
-      <c r="N113" s="216"/>
-      <c r="O113" s="216"/>
-      <c r="P113" s="216"/>
-      <c r="Q113" s="216"/>
-      <c r="R113" s="216"/>
-      <c r="S113" s="217"/>
+      <c r="F113" s="228"/>
+      <c r="G113" s="228"/>
+      <c r="H113" s="228"/>
+      <c r="I113" s="228"/>
+      <c r="J113" s="228"/>
+      <c r="K113" s="228"/>
+      <c r="L113" s="228"/>
+      <c r="M113" s="228"/>
+      <c r="N113" s="228"/>
+      <c r="O113" s="228"/>
+      <c r="P113" s="228"/>
+      <c r="Q113" s="228"/>
+      <c r="R113" s="228"/>
+      <c r="S113" s="229"/>
     </row>
     <row r="115" spans="5:19">
       <c r="E115" s="40" t="s">
@@ -9191,7 +9622,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{241BFFCF-883D-3C42-B761-0C4DF683252F}">
-  <dimension ref="B2:Z129"/>
+  <dimension ref="B2:Z209"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="2.83203125" customWidth="1"/>
@@ -10318,29 +10749,23 @@
       </c>
     </row>
     <row r="22" spans="2:25">
-      <c r="B22" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="25">
-        <v>43900</v>
-      </c>
-      <c r="E22" s="215" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="216"/>
-      <c r="G22" s="216"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="216"/>
-      <c r="J22" s="216"/>
-      <c r="K22" s="216"/>
-      <c r="L22" s="216"/>
-      <c r="M22" s="216"/>
-      <c r="N22" s="216"/>
-      <c r="O22" s="216"/>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="216"/>
-      <c r="R22" s="216"/>
-      <c r="S22" s="217"/>
+      <c r="E22" s="227" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="228"/>
+      <c r="G22" s="228"/>
+      <c r="H22" s="228"/>
+      <c r="I22" s="228"/>
+      <c r="J22" s="228"/>
+      <c r="K22" s="228"/>
+      <c r="L22" s="228"/>
+      <c r="M22" s="228"/>
+      <c r="N22" s="228"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="228"/>
+      <c r="Q22" s="228"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="229"/>
       <c r="V22" s="54">
         <f>Y22/V3</f>
         <v>5.8740540540540538</v>
@@ -10405,52 +10830,52 @@
         <v>0</v>
       </c>
       <c r="C25" s="8">
-        <v>0.53518929796793402</v>
+        <v>9.3012623676080902E-2</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F25" s="11">
-        <v>0.39333808477912902</v>
+        <v>0.63542333223758496</v>
       </c>
       <c r="G25" s="12">
-        <v>5.7335014463377403E-2</v>
+        <v>7.4202956071021398E-2</v>
       </c>
       <c r="H25" s="12">
-        <v>3.1938202468483202E-2</v>
+        <v>0.30442684328592401</v>
       </c>
       <c r="I25" s="12">
-        <v>8.5775416835740706E-2</v>
+        <v>0.36798457391940698</v>
       </c>
       <c r="J25" s="12">
-        <v>7.9671694629496002E-3</v>
+        <v>0.21389752631446601</v>
       </c>
       <c r="K25" s="12">
-        <v>5.4221537536206198E-2</v>
+        <v>0.42033448356569197</v>
       </c>
       <c r="L25" s="13">
-        <v>5.52612743728879E-2</v>
+        <v>0.173184033003251</v>
       </c>
       <c r="M25" s="11">
-        <v>6.9413874835648299E-3</v>
+        <v>2.1690428282764101E-3</v>
       </c>
       <c r="N25" s="12">
-        <v>3.2451297547875103E-2</v>
+        <v>3.5604459302614397E-2</v>
       </c>
       <c r="O25" s="12">
-        <v>3.72762350126525E-4</v>
+        <v>0.150514064744531</v>
       </c>
       <c r="P25" s="12">
-        <v>5.2964971157036501E-2</v>
+        <v>8.2956618674325106E-2</v>
       </c>
       <c r="Q25" s="12">
-        <v>3.1530141109194297E-2</v>
+        <v>5.3776874496326503E-2</v>
       </c>
       <c r="R25" s="12">
-        <v>6.5642164419937102E-2</v>
+        <v>0.14411654311291999</v>
       </c>
       <c r="S25" s="13">
-        <v>9.68346946735128E-2</v>
+        <v>0.11662985074307899</v>
       </c>
     </row>
     <row r="26" spans="2:25">
@@ -10458,52 +10883,52 @@
         <v>1</v>
       </c>
       <c r="C26" s="9">
-        <v>0.70256426484755097</v>
+        <v>6.0542914242030503E-2</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="14">
-        <v>4.1243283557498199E-2</v>
+        <v>8.9230719005575596E-2</v>
       </c>
       <c r="G26" s="15">
-        <v>0.37634718143700402</v>
+        <v>0.61650558689414503</v>
       </c>
       <c r="H26" s="15">
-        <v>1.7018291471972799E-2</v>
+        <v>0.13080370459023399</v>
       </c>
       <c r="I26" s="15">
-        <v>7.0032566206097893E-2</v>
+        <v>0.36943433929318198</v>
       </c>
       <c r="J26" s="15">
-        <v>3.49320987376166E-3</v>
+        <v>1.7736118456985099</v>
       </c>
       <c r="K26" s="15">
-        <v>4.3366917344522402E-2</v>
+        <v>0.388501310527959</v>
       </c>
       <c r="L26" s="16">
-        <v>7.9963648219744193E-2</v>
+        <v>0.36999424576822099</v>
       </c>
       <c r="M26" s="14">
-        <v>5.7575899393591701E-2</v>
+        <v>0.15038569514150499</v>
       </c>
       <c r="N26" s="15">
-        <v>1.9197961744020799E-2</v>
+        <v>8.1881216571179404E-4</v>
       </c>
       <c r="O26" s="15">
-        <v>3.0351318753288802E-2</v>
+        <v>6.1572577671600001E-2</v>
       </c>
       <c r="P26" s="15">
-        <v>-3.0116819052774101E-2</v>
+        <v>7.6740196453891699E-3</v>
       </c>
       <c r="Q26" s="15">
-        <v>-2.0028311064219798E-3</v>
+        <v>2.32129610157469E-8</v>
       </c>
       <c r="R26" s="15">
-        <v>6.2972875703747599E-2</v>
+        <v>4.3444483361352003E-2</v>
       </c>
       <c r="S26" s="16">
-        <v>9.5804098530645795E-2</v>
+        <v>5.3285623544847401E-2</v>
       </c>
     </row>
     <row r="27" spans="2:25">
@@ -10511,52 +10936,52 @@
         <v>2</v>
       </c>
       <c r="C27" s="9">
-        <v>0.104772667257835</v>
+        <v>3.2972156586063901E-2</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F27" s="14">
-        <v>2.4471903605458199E-3</v>
+        <v>5.1418478460116502E-3</v>
       </c>
       <c r="G27" s="15">
-        <v>6.7191827498578195E-4</v>
+        <v>1.4582785854327001E-3</v>
       </c>
       <c r="H27" s="15">
-        <v>7.4962453416156594E-2</v>
+        <v>0.37606219821034997</v>
       </c>
       <c r="I27" s="15">
-        <v>1.4978097676933901E-3</v>
+        <v>4.6896238875223798E-3</v>
       </c>
       <c r="J27" s="15">
-        <v>6.1566615586447397E-3</v>
+        <v>4.08908139807619E-2</v>
       </c>
       <c r="K27" s="15">
-        <v>-3.5595365562638199E-5</v>
+        <v>2.95737835590652E-2</v>
       </c>
       <c r="L27" s="16">
-        <v>-1.4982784980235599E-3</v>
+        <v>3.4621468587361999E-3</v>
       </c>
       <c r="M27" s="14">
-        <v>8.8187037875153305E-5</v>
+        <v>8.4985863201649697E-4</v>
       </c>
       <c r="N27" s="15">
-        <v>2.32829780879491E-3</v>
+        <v>3.8814174434889199E-3</v>
       </c>
       <c r="O27" s="15">
-        <v>-8.6233302318118295E-4</v>
+        <v>2.7039530100801599E-2</v>
       </c>
       <c r="P27" s="15">
-        <v>2.5651735819466801E-3</v>
+        <v>1.7970801043898699E-2</v>
       </c>
       <c r="Q27" s="15">
-        <v>5.5294980578047999E-3</v>
+        <v>0.39712279486378299</v>
       </c>
       <c r="R27" s="15">
-        <v>1.21448437078637E-3</v>
+        <v>8.5046201779194804E-3</v>
       </c>
       <c r="S27" s="16">
-        <v>8.7835188807947496E-4</v>
+        <v>4.2496176237725297E-4</v>
       </c>
     </row>
     <row r="28" spans="2:25">
@@ -10564,52 +10989,52 @@
         <v>3</v>
       </c>
       <c r="C28" s="9">
-        <v>7.4960988215726596E-2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="14">
-        <v>6.2226383180827597E-3</v>
+        <v>1.56533049644033E-2</v>
       </c>
       <c r="G28" s="15">
-        <v>4.9504951607491103E-3</v>
+        <v>6.0937322714270303E-3</v>
       </c>
       <c r="H28" s="15">
-        <v>1.7078345826599701E-3</v>
+        <v>5.0712921018914899E-2</v>
       </c>
       <c r="I28" s="15">
-        <v>-3.6075901851358801E-3</v>
+        <v>5.48011943279759E-15</v>
       </c>
       <c r="J28" s="15">
-        <v>3.3006925548922702E-3</v>
+        <v>9.0578916180052303E-25</v>
       </c>
       <c r="K28" s="15">
-        <v>9.4326811920502102E-2</v>
+        <v>0.38751502941399402</v>
       </c>
       <c r="L28" s="16">
-        <v>1.5478230926690401E-2</v>
+        <v>6.1897748018898101E-2</v>
       </c>
       <c r="M28" s="14">
-        <v>4.1146918057986702E-3</v>
+        <v>1.4754015879481601E-3</v>
       </c>
       <c r="N28" s="15">
-        <v>4.7622244242812896E-3</v>
+        <v>4.4438588901911098E-4</v>
       </c>
       <c r="O28" s="15">
-        <v>-2.5855480836690199E-4</v>
+        <v>1.91740848887535E-4</v>
       </c>
       <c r="P28" s="15">
-        <v>-7.6351775926445297E-4</v>
+        <v>8.1849063329694796E-5</v>
       </c>
       <c r="Q28" s="15">
-        <v>4.0278178828526698E-4</v>
+        <v>1.1821260846249201E-4</v>
       </c>
       <c r="R28" s="15">
-        <v>1.6262713816809701E-2</v>
+        <v>0.350752201245705</v>
       </c>
       <c r="S28" s="16">
-        <v>4.5347171390928601E-2</v>
+        <v>0.53761421355824501</v>
       </c>
     </row>
     <row r="29" spans="2:25">
@@ -10617,52 +11042,52 @@
         <v>4</v>
       </c>
       <c r="C29" s="9">
-        <v>2.2412680624724599E-2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="14">
-        <v>-9.5147050198429806E-5</v>
+        <v>2.9403862443621699E-3</v>
       </c>
       <c r="G29" s="15">
-        <v>1.9759123468192699E-4</v>
+        <v>1.55341559994053E-3</v>
       </c>
       <c r="H29" s="15">
-        <v>3.1122852090647202E-3</v>
+        <v>3.6851785625357597E-2</v>
       </c>
       <c r="I29" s="15">
-        <v>1.25135736058503E-3</v>
+        <v>1.98235120707424E-3</v>
       </c>
       <c r="J29" s="15">
-        <v>-5.9324822708124803E-3</v>
+        <v>2.5487579739181799E-2</v>
       </c>
       <c r="K29" s="15">
-        <v>3.1178409624240599E-3</v>
+        <v>1.17057392407842E-3</v>
       </c>
       <c r="L29" s="16">
-        <v>-7.5523759042768804E-4</v>
+        <v>6.7983402684474195E-7</v>
       </c>
       <c r="M29" s="14">
-        <v>1.7123687731292799E-4</v>
+        <v>2.8280069438156299E-3</v>
       </c>
       <c r="N29" s="15">
-        <v>2.5468109670667E-4</v>
+        <v>2.1051459254550998E-3</v>
       </c>
       <c r="O29" s="15">
-        <v>-5.9918335869714998E-4</v>
+        <v>1.247049644735E-2</v>
       </c>
       <c r="P29" s="15">
-        <v>4.3857797995441102E-4</v>
+        <v>3.03181088098783E-2</v>
       </c>
       <c r="Q29" s="15">
-        <v>1.7250074928351301E-3</v>
+        <v>3.2342959570012299E-2</v>
       </c>
       <c r="R29" s="15">
-        <v>5.5038115476256004E-4</v>
+        <v>6.4181239568624803E-3</v>
       </c>
       <c r="S29" s="16">
-        <v>3.6784800534303498E-4</v>
+        <v>7.8174705728247397E-4</v>
       </c>
     </row>
     <row r="30" spans="2:25">
@@ -10670,52 +11095,52 @@
         <v>5</v>
       </c>
       <c r="C30" s="9">
-        <v>5.1322646071090203E-2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="14">
-        <v>2.2835460302872601E-3</v>
+        <v>1.02601042751346E-2</v>
       </c>
       <c r="G30" s="15">
-        <v>5.2265817796300702E-4</v>
+        <v>2.8611992045363098E-3</v>
       </c>
       <c r="H30" s="15">
-        <v>2.1378141978207602E-2</v>
+        <v>0.113687950556132</v>
       </c>
       <c r="I30" s="15">
-        <v>-1.96109371734838E-3</v>
+        <v>2.7471974563581299E-2</v>
       </c>
       <c r="J30" s="15">
-        <v>-1.00963044765619E-3</v>
+        <v>8.9234143492994307E-3</v>
       </c>
       <c r="K30" s="15">
-        <v>-6.52284809838662E-4</v>
+        <v>1.9581054931155201E-3</v>
       </c>
       <c r="L30" s="16">
-        <v>-2.7341248495544798E-3</v>
+        <v>2.8852805552146002E-16</v>
       </c>
       <c r="M30" s="14">
-        <v>1.7778444072567601E-4</v>
+        <v>1.02568113623438E-3</v>
       </c>
       <c r="N30" s="15">
-        <v>2.5443357434615098E-3</v>
+        <v>1.4023815203163101E-3</v>
       </c>
       <c r="O30" s="15">
-        <v>-1.0751169224511E-4</v>
+        <v>6.2312318689419699E-3</v>
       </c>
       <c r="P30" s="15">
-        <v>1.0152654207394401E-2</v>
+        <v>0.177212260969868</v>
       </c>
       <c r="Q30" s="15">
-        <v>8.3493711327698797E-3</v>
+        <v>0.31270028141774803</v>
       </c>
       <c r="R30" s="15">
-        <v>-1.0472415122905899E-3</v>
+        <v>1.7748942415381799E-4</v>
       </c>
       <c r="S30" s="16">
-        <v>-6.6693234913382804E-4</v>
+        <v>4.65416275008186E-4</v>
       </c>
     </row>
     <row r="31" spans="2:25">
@@ -10723,52 +11148,52 @@
         <v>6</v>
       </c>
       <c r="C31" s="10">
-        <v>3.3017824876450899E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="17">
-        <v>3.6684213933323101E-3</v>
+        <v>6.0088650570535697E-3</v>
       </c>
       <c r="G31" s="18">
-        <v>1.7434283524032899E-3</v>
+        <v>3.6338521117513598E-3</v>
       </c>
       <c r="H31" s="18">
-        <v>2.5334860631527501E-3</v>
+        <v>2.8264726630657201E-2</v>
       </c>
       <c r="I31" s="18">
-        <v>-2.31259904188605E-4</v>
+        <v>8.2233748521931798E-4</v>
       </c>
       <c r="J31" s="18">
-        <v>-1.8399282758147901E-3</v>
+        <v>1.04808253060165E-3</v>
       </c>
       <c r="K31" s="18">
-        <v>-7.3799606772789197E-4</v>
+        <v>1.13860652730718E-4</v>
       </c>
       <c r="L31" s="19">
-        <v>-3.7638981638834202E-3</v>
+        <v>3.4813781925803699E-3</v>
       </c>
       <c r="M31" s="17">
-        <v>-6.5616434783010802E-4</v>
+        <v>1.0442547167245601E-5</v>
       </c>
       <c r="N31" s="18">
-        <v>3.08463214715052E-3</v>
+        <v>3.9591768003668698E-4</v>
       </c>
       <c r="O31" s="18">
-        <v>-1.12493483439554E-3</v>
+        <v>6.7227433478349297E-4</v>
       </c>
       <c r="P31" s="18">
-        <v>5.60558175961067E-2</v>
+        <v>0.281770546463323</v>
       </c>
       <c r="Q31" s="18">
-        <v>8.9657628964895496E-3</v>
+        <v>4.1782398837187998E-2</v>
       </c>
       <c r="R31" s="18">
-        <v>4.3054136961228901E-4</v>
+        <v>6.6119489748626793E-5</v>
       </c>
       <c r="S31" s="19">
-        <v>6.3636681013586104E-4</v>
+        <v>1.2396412831661E-4</v>
       </c>
     </row>
     <row r="32" spans="2:25">
@@ -10776,52 +11201,52 @@
         <v>7</v>
       </c>
       <c r="C32" s="8">
-        <v>0.59216568065030994</v>
+        <v>9.5126800871421099E-2</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="11">
-        <v>1.35688431217747E-2</v>
+        <v>2.2105085322456598E-3</v>
       </c>
       <c r="G32" s="12">
-        <v>3.4575642010581199E-2</v>
+        <v>3.8498269352215703E-2</v>
       </c>
       <c r="H32" s="12">
-        <v>1.1625969525522199E-3</v>
+        <v>0.148428096939971</v>
       </c>
       <c r="I32" s="12">
-        <v>7.9251438227665297E-2</v>
+        <v>8.4912570009538002E-2</v>
       </c>
       <c r="J32" s="12">
-        <v>2.5117668914954601E-2</v>
+        <v>3.9514783378672702E-2</v>
       </c>
       <c r="K32" s="12">
-        <v>8.1599348631065202E-2</v>
+        <v>0.136643898780063</v>
       </c>
       <c r="L32" s="13">
-        <v>0.127761143591787</v>
+        <v>0.120180000919044</v>
       </c>
       <c r="M32" s="11">
-        <v>0.413192260430645</v>
+        <v>0.65806491048195104</v>
       </c>
       <c r="N32" s="12">
-        <v>5.2822098015012697E-2</v>
+        <v>7.9517891241321997E-2</v>
       </c>
       <c r="O32" s="12">
-        <v>3.8072845669722299E-2</v>
+        <v>0.31628214822228701</v>
       </c>
       <c r="P32" s="12">
-        <v>7.0582725192768203E-2</v>
+        <v>0.35591580605775602</v>
       </c>
       <c r="Q32" s="12">
-        <v>1.9378310882524698E-2</v>
+        <v>0.24409979474744301</v>
       </c>
       <c r="R32" s="12">
-        <v>6.0522712339790001E-2</v>
+        <v>0.45045431151536802</v>
       </c>
       <c r="S32" s="13">
-        <v>7.3938152952921096E-2</v>
+        <v>0.186013561921757</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -10829,52 +11254,52 @@
         <v>8</v>
       </c>
       <c r="C33" s="9">
-        <v>0.62874022819505004</v>
+        <v>5.82206055234087E-2</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="14">
-        <v>5.5635054663094097E-2</v>
+        <v>0.141139775425663</v>
       </c>
       <c r="G33" s="15">
-        <v>1.45272127107367E-2</v>
+        <v>9.1094794054436001E-4</v>
       </c>
       <c r="H33" s="15">
-        <v>2.6291449661879799E-2</v>
+        <v>5.2513181256030703E-2</v>
       </c>
       <c r="I33" s="15">
-        <v>-3.5524753203823603E-2</v>
+        <v>8.1271411922248602E-3</v>
       </c>
       <c r="J33" s="15">
-        <v>-3.96929986071124E-3</v>
+        <v>7.1130579519545405E-11</v>
       </c>
       <c r="K33" s="15">
-        <v>5.2769505136874499E-2</v>
+        <v>4.4255506900302E-2</v>
       </c>
       <c r="L33" s="16">
-        <v>6.1220459023021701E-2</v>
+        <v>4.6236256418184803E-2</v>
       </c>
       <c r="M33" s="14">
-        <v>4.7776080707363902E-2</v>
+        <v>8.3287863028452799E-2</v>
       </c>
       <c r="N33" s="15">
-        <v>0.36697475223225601</v>
+        <v>0.61151096231939905</v>
       </c>
       <c r="O33" s="15">
-        <v>8.5339458163966996E-3</v>
+        <v>0.12646944283579001</v>
       </c>
       <c r="P33" s="15">
-        <v>7.1103108360798903E-2</v>
+        <v>0.33351322144946599</v>
       </c>
       <c r="Q33" s="15">
-        <v>1.6702642200636299E-2</v>
+        <v>1.74815412397333</v>
       </c>
       <c r="R33" s="15">
-        <v>4.1031060816339997E-2</v>
+        <v>0.38539122289382099</v>
       </c>
       <c r="S33" s="16">
-        <v>7.9504899077649002E-2</v>
+        <v>0.34907390617842399</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -10882,52 +11307,52 @@
         <v>9</v>
       </c>
       <c r="C34" s="9">
-        <v>9.2683657765842406E-2</v>
+        <v>3.0697387630630301E-2</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="14">
-        <v>4.2824322408129901E-4</v>
+        <v>7.7560628335939603E-4</v>
       </c>
       <c r="G34" s="15">
-        <v>2.3081217243233199E-3</v>
+        <v>4.4630452853871997E-3</v>
       </c>
       <c r="H34" s="15">
-        <v>6.8291351766502104E-4</v>
+        <v>2.4140460519625598E-2</v>
       </c>
       <c r="I34" s="15">
-        <v>1.3504545393826701E-3</v>
+        <v>1.60096811399453E-2</v>
       </c>
       <c r="J34" s="15">
-        <v>2.7953213566203798E-3</v>
+        <v>0.39499792295603497</v>
       </c>
       <c r="K34" s="15">
-        <v>1.12952027321433E-3</v>
+        <v>4.9466299342883603E-3</v>
       </c>
       <c r="L34" s="16">
-        <v>-1.49288730011319E-3</v>
+        <v>1.3582278660787101E-3</v>
       </c>
       <c r="M34" s="14">
-        <v>2.1717834754169801E-3</v>
+        <v>5.04772818132388E-3</v>
       </c>
       <c r="N34" s="15">
-        <v>7.1597887373547897E-4</v>
+        <v>1.60850104219744E-3</v>
       </c>
       <c r="O34" s="15">
-        <v>6.8505805444524101E-2</v>
+        <v>0.38182372558079902</v>
       </c>
       <c r="P34" s="15">
-        <v>-6.1617667759344302E-4</v>
+        <v>4.1095745196469101E-3</v>
       </c>
       <c r="Q34" s="15">
-        <v>1.06249174366454E-2</v>
+        <v>3.4211309917064003E-2</v>
       </c>
       <c r="R34" s="15">
-        <v>4.3415718582100003E-3</v>
+        <v>3.5769859399603803E-2</v>
       </c>
       <c r="S34" s="16">
-        <v>-2.69330622343106E-3</v>
+        <v>3.0794608588509101E-3</v>
       </c>
     </row>
     <row r="35" spans="2:26">
@@ -10935,52 +11360,52 @@
         <v>10</v>
       </c>
       <c r="C35" s="9">
-        <v>7.4347006034703095E-2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="14">
-        <v>5.2763906954544498E-3</v>
+        <v>1.84011015202333E-3</v>
       </c>
       <c r="G35" s="15">
-        <v>3.6308283292819602E-3</v>
+        <v>4.1727795602479603E-4</v>
       </c>
       <c r="H35" s="15">
-        <v>-3.9376790106783601E-4</v>
+        <v>3.0104511395013899E-4</v>
       </c>
       <c r="I35" s="15">
-        <v>-2.18389786410342E-4</v>
+        <v>6.7906223675399498E-6</v>
       </c>
       <c r="J35" s="15">
-        <v>1.7870627967296201E-3</v>
+        <v>7.5068184988049899E-7</v>
       </c>
       <c r="K35" s="15">
-        <v>1.0145107295558699E-2</v>
+        <v>0.35037717849408201</v>
       </c>
       <c r="L35" s="16">
-        <v>3.4601601979008599E-2</v>
+        <v>0.55224558220145803</v>
       </c>
       <c r="M35" s="14">
-        <v>5.6739593864322804E-3</v>
+        <v>1.38174156765627E-2</v>
       </c>
       <c r="N35" s="15">
-        <v>4.8573308692465003E-3</v>
+        <v>7.3786223016321598E-3</v>
       </c>
       <c r="O35" s="15">
-        <v>7.9599376850471998E-3</v>
+        <v>4.8743605893939897E-2</v>
       </c>
       <c r="P35" s="15">
-        <v>-6.85569246833508E-3</v>
+        <v>1.1394896839512401E-4</v>
       </c>
       <c r="Q35" s="15">
-        <v>-1.85377325126083E-3</v>
+        <v>1.33316064668517E-24</v>
       </c>
       <c r="R35" s="15">
-        <v>0.11994143703609</v>
+        <v>0.40011734786285802</v>
       </c>
       <c r="S35" s="16">
-        <v>1.6599085609855201E-2</v>
+        <v>6.2507781099067197E-2</v>
       </c>
     </row>
     <row r="36" spans="2:26">
@@ -10988,52 +11413,52 @@
         <v>11</v>
       </c>
       <c r="C36" s="9">
-        <v>2.2015558423844599E-2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="14">
-        <v>1.1311847741901101E-4</v>
+        <v>3.04456064154304E-3</v>
       </c>
       <c r="G36" s="15">
-        <v>3.5260817651005399E-4</v>
+        <v>1.8232238727128201E-3</v>
       </c>
       <c r="H36" s="15">
-        <v>2.0670601367960901E-4</v>
+        <v>1.2900175401594299E-2</v>
       </c>
       <c r="I36" s="15">
-        <v>4.1787836017759799E-3</v>
+        <v>3.0823577990383801E-2</v>
       </c>
       <c r="J36" s="15">
-        <v>4.3663951882746601E-3</v>
+        <v>3.3615598288396498E-2</v>
       </c>
       <c r="K36" s="15">
-        <v>1.92850154646537E-4</v>
+        <v>3.8761127349210998E-3</v>
       </c>
       <c r="L36" s="16">
-        <v>-1.30660910837738E-3</v>
+        <v>1.4143964432390399E-3</v>
       </c>
       <c r="M36" s="14">
-        <v>3.5673120954519602E-4</v>
+        <v>2.78566502062246E-3</v>
       </c>
       <c r="N36" s="15">
-        <v>2.74063476377948E-4</v>
+        <v>1.89520539068656E-3</v>
       </c>
       <c r="O36" s="15">
-        <v>2.0479158502291901E-4</v>
+        <v>3.4912096421011597E-2</v>
       </c>
       <c r="P36" s="15">
-        <v>1.2924735981037301E-3</v>
+        <v>2.54953402102E-3</v>
       </c>
       <c r="Q36" s="15">
-        <v>-5.1469385806720397E-4</v>
+        <v>2.7435610834954698E-2</v>
       </c>
       <c r="R36" s="15">
-        <v>-2.0207781220306801E-4</v>
+        <v>9.95933754708539E-4</v>
       </c>
       <c r="S36" s="16">
-        <v>1.3155710503089499E-3</v>
+        <v>1.97404640587719E-4</v>
       </c>
     </row>
     <row r="37" spans="2:26">
@@ -11041,52 +11466,52 @@
         <v>12</v>
       </c>
       <c r="C37" s="9">
-        <v>5.1229536490832499E-2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="14">
-        <v>-8.3029086270789402E-5</v>
+        <v>1.29923860031023E-3</v>
       </c>
       <c r="G37" s="15">
-        <v>2.4329996221480899E-3</v>
+        <v>1.43760441082397E-3</v>
       </c>
       <c r="H37" s="15">
-        <v>1.5086518017022701E-3</v>
+        <v>5.5535382487360199E-3</v>
       </c>
       <c r="I37" s="15">
-        <v>8.1474314522958103E-3</v>
+        <v>0.175721798026308</v>
       </c>
       <c r="J37" s="15">
-        <v>1.0770596860246499E-2</v>
+        <v>0.30893349844993201</v>
       </c>
       <c r="K37" s="15">
-        <v>-1.5767392840354601E-4</v>
+        <v>4.5334911104964103E-4</v>
       </c>
       <c r="L37" s="16">
-        <v>5.7046956937316503E-4</v>
+        <v>2.5512546437385202E-4</v>
       </c>
       <c r="M37" s="14">
-        <v>2.1136916570541702E-3</v>
+        <v>8.8853525256193198E-3</v>
       </c>
       <c r="N37" s="15">
-        <v>2.64925242268868E-4</v>
+        <v>3.0829624910288398E-3</v>
       </c>
       <c r="O37" s="15">
-        <v>3.5690077588397998E-2</v>
+        <v>0.116184053885766</v>
       </c>
       <c r="P37" s="15">
-        <v>7.2654834095284998E-4</v>
+        <v>2.9444038534390999E-2</v>
       </c>
       <c r="Q37" s="15">
-        <v>-2.5234115831993401E-3</v>
+        <v>8.8603316919929499E-3</v>
       </c>
       <c r="R37" s="15">
-        <v>8.71458269321181E-4</v>
+        <v>3.0587833356993601E-3</v>
       </c>
       <c r="S37" s="16">
-        <v>-3.4328866561506699E-4</v>
+        <v>8.6845996727331895E-6</v>
       </c>
     </row>
     <row r="38" spans="2:26">
@@ -11094,72 +11519,72 @@
         <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>3.3387290187160398E-2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="17">
-        <v>-4.8920141254981699E-4</v>
+        <v>3.8851294717226099E-5</v>
       </c>
       <c r="G38" s="18">
-        <v>2.3817776077362401E-3</v>
+        <v>3.3774217981684997E-4</v>
       </c>
       <c r="H38" s="18">
-        <v>5.0702294071367404E-4</v>
+        <v>5.7877975455291101E-4</v>
       </c>
       <c r="I38" s="18">
-        <v>5.8433089635560098E-2</v>
+        <v>0.27698252185564598</v>
       </c>
       <c r="J38" s="18">
-        <v>3.0191106587354201E-3</v>
+        <v>3.7033443461341797E-2</v>
       </c>
       <c r="K38" s="18">
-        <v>-7.96807645734532E-4</v>
+        <v>1.68109593556366E-4</v>
       </c>
       <c r="L38" s="19">
-        <v>-1.5040310900077301E-3</v>
+        <v>2.60797504786109E-9</v>
       </c>
       <c r="M38" s="17">
-        <v>2.84353610725065E-3</v>
+        <v>5.7280770249319504E-3</v>
       </c>
       <c r="N38" s="18">
-        <v>2.0112317258197399E-3</v>
+        <v>3.9133759871972304E-3</v>
       </c>
       <c r="O38" s="18">
-        <v>3.6901139167655902E-3</v>
+        <v>2.58904709977744E-2</v>
       </c>
       <c r="P38" s="18">
-        <v>-5.3094750092724005E-4</v>
+        <v>6.2784661643452597E-4</v>
       </c>
       <c r="Q38" s="18">
-        <v>-2.1551030119677699E-3</v>
+        <v>1.8291085122382599E-3</v>
       </c>
       <c r="R38" s="18">
-        <v>-2.2540350058386301E-3</v>
+        <v>1.78708355887285E-4</v>
       </c>
       <c r="S38" s="19">
-        <v>-3.7351946564871102E-3</v>
+        <v>3.41146113832486E-3</v>
       </c>
     </row>
     <row r="41" spans="2:26">
-      <c r="E41" s="215" t="s">
+      <c r="E41" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="216"/>
-      <c r="G41" s="216"/>
-      <c r="H41" s="216"/>
-      <c r="I41" s="216"/>
-      <c r="J41" s="216"/>
-      <c r="K41" s="216"/>
-      <c r="L41" s="216"/>
-      <c r="M41" s="216"/>
-      <c r="N41" s="216"/>
-      <c r="O41" s="216"/>
-      <c r="P41" s="216"/>
-      <c r="Q41" s="216"/>
-      <c r="R41" s="216"/>
-      <c r="S41" s="217"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="228"/>
+      <c r="Q41" s="228"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="229"/>
     </row>
     <row r="43" spans="2:26">
       <c r="E43" s="40" t="s">
@@ -11938,23 +12363,23 @@
       </c>
     </row>
     <row r="59" spans="5:26">
-      <c r="E59" s="215" t="s">
+      <c r="E59" s="227" t="s">
         <v>34</v>
       </c>
-      <c r="F59" s="216"/>
-      <c r="G59" s="216"/>
-      <c r="H59" s="216"/>
-      <c r="I59" s="216"/>
-      <c r="J59" s="216"/>
-      <c r="K59" s="216"/>
-      <c r="L59" s="216"/>
-      <c r="M59" s="216"/>
-      <c r="N59" s="216"/>
-      <c r="O59" s="216"/>
-      <c r="P59" s="216"/>
-      <c r="Q59" s="216"/>
-      <c r="R59" s="216"/>
-      <c r="S59" s="217"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="228"/>
+      <c r="H59" s="228"/>
+      <c r="I59" s="228"/>
+      <c r="J59" s="228"/>
+      <c r="K59" s="228"/>
+      <c r="L59" s="228"/>
+      <c r="M59" s="228"/>
+      <c r="N59" s="228"/>
+      <c r="O59" s="228"/>
+      <c r="P59" s="228"/>
+      <c r="Q59" s="228"/>
+      <c r="R59" s="228"/>
+      <c r="S59" s="229"/>
     </row>
     <row r="61" spans="5:26">
       <c r="E61" s="40" t="s">
@@ -12810,23 +13235,23 @@
       </c>
     </row>
     <row r="77" spans="5:25">
-      <c r="E77" s="215" t="s">
+      <c r="E77" s="227" t="s">
         <v>35</v>
       </c>
-      <c r="F77" s="216"/>
-      <c r="G77" s="216"/>
-      <c r="H77" s="216"/>
-      <c r="I77" s="216"/>
-      <c r="J77" s="216"/>
-      <c r="K77" s="216"/>
-      <c r="L77" s="216"/>
-      <c r="M77" s="216"/>
-      <c r="N77" s="216"/>
-      <c r="O77" s="216"/>
-      <c r="P77" s="216"/>
-      <c r="Q77" s="216"/>
-      <c r="R77" s="216"/>
-      <c r="S77" s="217"/>
+      <c r="F77" s="228"/>
+      <c r="G77" s="228"/>
+      <c r="H77" s="228"/>
+      <c r="I77" s="228"/>
+      <c r="J77" s="228"/>
+      <c r="K77" s="228"/>
+      <c r="L77" s="228"/>
+      <c r="M77" s="228"/>
+      <c r="N77" s="228"/>
+      <c r="O77" s="228"/>
+      <c r="P77" s="228"/>
+      <c r="Q77" s="228"/>
+      <c r="R77" s="228"/>
+      <c r="S77" s="229"/>
       <c r="V77" s="54">
         <f>Y77/V$3</f>
         <v>5.8057357357357358</v>
@@ -13545,23 +13970,23 @@
       </c>
     </row>
     <row r="95" spans="5:19">
-      <c r="E95" s="215" t="s">
+      <c r="E95" s="227" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="216"/>
-      <c r="G95" s="216"/>
-      <c r="H95" s="216"/>
-      <c r="I95" s="216"/>
-      <c r="J95" s="216"/>
-      <c r="K95" s="216"/>
-      <c r="L95" s="216"/>
-      <c r="M95" s="216"/>
-      <c r="N95" s="216"/>
-      <c r="O95" s="216"/>
-      <c r="P95" s="216"/>
-      <c r="Q95" s="216"/>
-      <c r="R95" s="216"/>
-      <c r="S95" s="217"/>
+      <c r="F95" s="228"/>
+      <c r="G95" s="228"/>
+      <c r="H95" s="228"/>
+      <c r="I95" s="228"/>
+      <c r="J95" s="228"/>
+      <c r="K95" s="228"/>
+      <c r="L95" s="228"/>
+      <c r="M95" s="228"/>
+      <c r="N95" s="228"/>
+      <c r="O95" s="228"/>
+      <c r="P95" s="228"/>
+      <c r="Q95" s="228"/>
+      <c r="R95" s="228"/>
+      <c r="S95" s="229"/>
     </row>
     <row r="97" spans="5:19">
       <c r="E97" s="40" t="s">
@@ -14209,672 +14634,3897 @@
       <c r="S111" s="19"/>
     </row>
     <row r="113" spans="5:19">
-      <c r="E113" s="215" t="s">
-        <v>38</v>
-      </c>
-      <c r="F113" s="216"/>
-      <c r="G113" s="216"/>
-      <c r="H113" s="216"/>
-      <c r="I113" s="216"/>
-      <c r="J113" s="216"/>
-      <c r="K113" s="216"/>
-      <c r="L113" s="216"/>
-      <c r="M113" s="216"/>
-      <c r="N113" s="216"/>
-      <c r="O113" s="216"/>
-      <c r="P113" s="216"/>
-      <c r="Q113" s="216"/>
-      <c r="R113" s="216"/>
-      <c r="S113" s="217"/>
+      <c r="E113" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F113" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G113" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H113" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I113" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J113" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K113" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L113" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M113" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N113" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O113" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P113" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q113" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R113" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S113" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="5:19">
+      <c r="E114" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F114" s="29">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L114" s="33">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M114" s="29">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O114" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="P114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R114" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S114" s="33">
+        <v>1.0000000000000001E-5</v>
+      </c>
     </row>
     <row r="115" spans="5:19">
-      <c r="E115" s="40" t="s">
-        <v>21</v>
-      </c>
-      <c r="F115" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="G115" s="42" t="s">
+      <c r="E115" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="H115" s="42" t="s">
+      <c r="F115" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J115" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="K115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L115" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M115" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P115" s="215"/>
+      <c r="Q115" s="215"/>
+      <c r="R115" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S115" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="116" spans="5:19">
+      <c r="E116" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="I115" s="42" t="s">
-        <v>3</v>
-      </c>
-      <c r="J115" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="K115" s="42" t="s">
-        <v>5</v>
-      </c>
-      <c r="L115" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="M115" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="N115" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="O115" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="P115" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q115" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="R115" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="S115" s="43" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="116" spans="5:19">
-      <c r="E116" s="44" t="s">
-        <v>0</v>
-      </c>
-      <c r="F116" s="206">
-        <v>9.9905462085300697E-2</v>
-      </c>
-      <c r="G116" s="207">
-        <v>-7.2601803864568104E-2</v>
-      </c>
-      <c r="H116" s="207">
-        <v>3.3104325729460801E-2</v>
-      </c>
-      <c r="I116" s="207">
-        <v>-0.384545089398381</v>
-      </c>
-      <c r="J116" s="207">
-        <v>-0.32985234713682898</v>
-      </c>
-      <c r="K116" s="207">
-        <v>-0.15127604366056699</v>
-      </c>
-      <c r="L116" s="208">
-        <v>-0.168260848967065</v>
-      </c>
-      <c r="M116" s="206">
-        <v>-6.80338487428752E-2</v>
-      </c>
-      <c r="N116" s="207">
-        <v>6.1727562713571403E-2</v>
-      </c>
-      <c r="O116" s="207">
-        <v>-0.184205855358412</v>
-      </c>
-      <c r="P116" s="207">
-        <v>0.36603130909763198</v>
-      </c>
-      <c r="Q116" s="207">
-        <v>0.298722828774653</v>
-      </c>
-      <c r="R116" s="207">
-        <v>-0.109675134137715</v>
-      </c>
-      <c r="S116" s="208">
-        <v>8.4202653872626598E-2</v>
+      <c r="F116" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G116" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="H116" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I116" s="30">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="J116" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K116" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L116" s="34">
+        <v>1.9186000000000002E-2</v>
+      </c>
+      <c r="M116" s="32">
+        <v>2E-3</v>
+      </c>
+      <c r="N116" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O116" s="30">
+        <v>8.8859999999999998E-3</v>
+      </c>
+      <c r="P116" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="Q116" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="R116" s="30">
+        <v>2.4301E-2</v>
+      </c>
+      <c r="S116" s="34">
+        <v>1.8100000000000002E-2</v>
       </c>
     </row>
     <row r="117" spans="5:19">
       <c r="E117" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="F117" s="209">
-        <v>-8.1173198711979894E-2</v>
-      </c>
-      <c r="G117" s="210">
-        <v>-0.176773261280325</v>
-      </c>
-      <c r="H117" s="210">
-        <v>-5.1934771054012504E-3</v>
-      </c>
-      <c r="I117" s="210">
-        <v>-0.40068279512885502</v>
-      </c>
-      <c r="J117" s="210">
-        <v>-0.25984604752915602</v>
-      </c>
-      <c r="K117" s="210">
-        <v>-0.120545263866407</v>
-      </c>
-      <c r="L117" s="211">
-        <v>-0.18571041586088999</v>
-      </c>
-      <c r="M117" s="209">
-        <v>-0.132620596724013</v>
-      </c>
-      <c r="N117" s="210">
-        <v>-4.4729627382706902E-2</v>
-      </c>
-      <c r="O117" s="210">
-        <v>-0.205072645035279</v>
-      </c>
-      <c r="P117" s="210"/>
-      <c r="Q117" s="210"/>
-      <c r="R117" s="210">
-        <v>-5.5175502387183703E-2</v>
-      </c>
-      <c r="S117" s="211">
-        <v>2.6651717174692498E-2</v>
+        <v>3</v>
+      </c>
+      <c r="F117" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G117" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H117" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I117" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J117" s="215"/>
+      <c r="K117" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L117" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M117" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N117" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O117" s="30">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="P117" s="225">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q117" s="215"/>
+      <c r="R117" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S117" s="34">
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="118" spans="5:19">
       <c r="E118" s="45" t="s">
-        <v>2</v>
-      </c>
-      <c r="F118" s="209">
-        <v>3.3159195074470599E-2</v>
-      </c>
-      <c r="G118" s="210">
-        <v>-7.7078482383726304E-2</v>
-      </c>
-      <c r="H118" s="210">
-        <v>0.10829855369722401</v>
-      </c>
-      <c r="I118" s="210">
-        <v>-0.390948541971536</v>
-      </c>
-      <c r="J118" s="210">
-        <v>-0.19486807230709599</v>
-      </c>
-      <c r="K118" s="210">
-        <v>-0.14538102977964101</v>
-      </c>
-      <c r="L118" s="211">
-        <v>-0.21446674640934801</v>
-      </c>
-      <c r="M118" s="209">
-        <v>1.23261300307289E-2</v>
-      </c>
-      <c r="N118" s="210">
-        <v>8.1821481175145996E-2</v>
-      </c>
-      <c r="O118" s="210">
-        <v>-8.0032070231368893E-2</v>
-      </c>
-      <c r="P118" s="210">
-        <v>0.34496642484183798</v>
-      </c>
-      <c r="Q118" s="210">
-        <v>0.24975132998221899</v>
-      </c>
-      <c r="R118" s="210">
-        <v>-1.2894031578603299E-2</v>
-      </c>
-      <c r="S118" s="211">
-        <v>9.3962488834249305E-2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F118" s="32">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="G118" s="30">
+        <v>1.499E-2</v>
+      </c>
+      <c r="H118" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I118" s="215">
+        <v>7.4368000000000004E-2</v>
+      </c>
+      <c r="J118" s="215"/>
+      <c r="K118" s="215"/>
+      <c r="L118" s="216"/>
+      <c r="M118" s="32">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="N118" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="O118" s="30">
+        <v>0.49580000000000002</v>
+      </c>
+      <c r="P118" s="30">
+        <v>9.7199999999999999E-4</v>
+      </c>
+      <c r="Q118" s="215">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R118" s="215">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="S118" s="216"/>
     </row>
     <row r="119" spans="5:19">
       <c r="E119" s="45" t="s">
-        <v>3</v>
-      </c>
-      <c r="F119" s="209">
-        <v>3.1985990939469501E-2</v>
-      </c>
-      <c r="G119" s="210">
-        <v>2.28579145681252E-2</v>
-      </c>
-      <c r="H119" s="210">
-        <v>3.8789976135843299E-2</v>
-      </c>
-      <c r="I119" s="210">
-        <v>0</v>
-      </c>
-      <c r="J119" s="210"/>
-      <c r="K119" s="210">
-        <v>-2.49383769471671E-3</v>
-      </c>
-      <c r="L119" s="211">
-        <v>-5.7678642737837897E-2</v>
-      </c>
-      <c r="M119" s="209">
-        <v>7.4148555518791598E-2</v>
-      </c>
-      <c r="N119" s="210">
-        <v>0.106569445993788</v>
-      </c>
-      <c r="O119" s="210">
-        <v>1.2328042328042301E-2</v>
-      </c>
-      <c r="P119" s="210">
-        <v>0.36558225170138697</v>
-      </c>
-      <c r="Q119" s="210"/>
-      <c r="R119" s="210">
-        <v>0.134094410099142</v>
-      </c>
-      <c r="S119" s="211">
-        <v>0.145409445815848</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="F119" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G119" s="30">
+        <v>9.7300000000000002E-4</v>
+      </c>
+      <c r="H119" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I119" s="215">
+        <v>1.78E-2</v>
+      </c>
+      <c r="J119" s="215"/>
+      <c r="K119" s="215">
+        <v>2E-3</v>
+      </c>
+      <c r="L119" s="216"/>
+      <c r="M119" s="32">
+        <v>1.588E-3</v>
+      </c>
+      <c r="N119" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O119" s="30">
+        <v>6.3920000000000001E-3</v>
+      </c>
+      <c r="P119" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="Q119" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="R119" s="215"/>
+      <c r="S119" s="216"/>
     </row>
     <row r="120" spans="5:19">
-      <c r="E120" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="F120" s="209">
-        <v>0.19694921070167601</v>
-      </c>
-      <c r="G120" s="210">
-        <v>0.120979461180703</v>
-      </c>
-      <c r="H120" s="210">
-        <v>0.28487052413991099</v>
-      </c>
-      <c r="I120" s="210">
-        <v>-0.36103413494717801</v>
-      </c>
-      <c r="J120" s="210"/>
-      <c r="K120" s="210"/>
-      <c r="L120" s="211"/>
-      <c r="M120" s="209">
-        <v>0.115933945367974</v>
-      </c>
-      <c r="N120" s="210">
-        <v>0.20617675130274299</v>
-      </c>
-      <c r="O120" s="210">
-        <v>2.69405539993775E-2</v>
-      </c>
-      <c r="P120" s="210">
-        <v>0.39425803969509099</v>
-      </c>
-      <c r="Q120" s="210">
-        <v>0.41304347826086901</v>
-      </c>
-      <c r="R120" s="210">
-        <v>-3.8461538461538401E-2</v>
-      </c>
-      <c r="S120" s="211"/>
+      <c r="E120" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="37">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G120" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H120" s="36">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="I120" s="217"/>
+      <c r="J120" s="217">
+        <v>1E-3</v>
+      </c>
+      <c r="K120" s="217"/>
+      <c r="L120" s="218">
+        <v>1E-3</v>
+      </c>
+      <c r="M120" s="224"/>
+      <c r="N120" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O120" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P120" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q120" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R120" s="217">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S120" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
     </row>
     <row r="121" spans="5:19">
-      <c r="E121" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="F121" s="209">
-        <v>0.33908320674796699</v>
-      </c>
-      <c r="G121" s="210">
-        <v>0.23677356768543401</v>
-      </c>
-      <c r="H121" s="210">
-        <v>0.32954592453568798</v>
-      </c>
-      <c r="I121" s="210">
-        <v>-0.279464285714285</v>
-      </c>
-      <c r="J121" s="210"/>
-      <c r="K121" s="210">
-        <v>0.35714285714285698</v>
-      </c>
-      <c r="L121" s="211"/>
-      <c r="M121" s="209">
-        <v>0.13035594497073599</v>
-      </c>
-      <c r="N121" s="210">
-        <v>0.34376156091940602</v>
-      </c>
-      <c r="O121" s="210">
-        <v>0.19541489470282</v>
-      </c>
-      <c r="P121" s="210">
-        <v>0.40244432902765298</v>
-      </c>
-      <c r="Q121" s="210">
-        <v>0.41224468679849002</v>
-      </c>
-      <c r="R121" s="210"/>
-      <c r="S121" s="211"/>
+      <c r="E121" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F121" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H121" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="I121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L121" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M121" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R121" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S121" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
     </row>
     <row r="122" spans="5:19">
-      <c r="E122" s="46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F122" s="212">
-        <v>0.38992800887755702</v>
-      </c>
-      <c r="G122" s="213">
-        <v>0.357343879573842</v>
-      </c>
-      <c r="H122" s="213">
-        <v>0.35695961707289903</v>
-      </c>
-      <c r="I122" s="213"/>
-      <c r="J122" s="213">
-        <v>0</v>
-      </c>
-      <c r="K122" s="213"/>
-      <c r="L122" s="214">
-        <v>0.3</v>
-      </c>
-      <c r="M122" s="212"/>
-      <c r="N122" s="213">
-        <v>0.38542534102252002</v>
-      </c>
-      <c r="O122" s="213">
-        <v>0.248404681738015</v>
-      </c>
-      <c r="P122" s="213">
-        <v>0.39877648109313402</v>
-      </c>
-      <c r="Q122" s="213">
-        <v>0.39245611541791697</v>
-      </c>
-      <c r="R122" s="213">
-        <v>0.28125</v>
-      </c>
-      <c r="S122" s="214">
-        <v>0.44999999999999901</v>
+      <c r="E122" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I122" s="219"/>
+      <c r="J122" s="219"/>
+      <c r="K122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L122" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M122" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O122" s="15">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="P122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q122" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="R122" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S122" s="16">
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="123" spans="5:19">
-      <c r="E123" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F123" s="80">
-        <v>4.1586665171067003E-2</v>
-      </c>
-      <c r="G123" s="81">
-        <v>-8.4605593533508897E-2</v>
-      </c>
-      <c r="H123" s="81">
-        <v>0.12356175481079799</v>
-      </c>
-      <c r="I123" s="81">
-        <v>-0.36471606551218499</v>
-      </c>
-      <c r="J123" s="81">
-        <v>-0.33753575166835897</v>
-      </c>
-      <c r="K123" s="81">
-        <v>7.2770796237683996E-2</v>
-      </c>
-      <c r="L123" s="82">
-        <v>-0.13257378720835999</v>
-      </c>
-      <c r="M123" s="80">
-        <v>-0.117936186435812</v>
-      </c>
-      <c r="N123" s="81">
-        <v>4.2214444254743397E-2</v>
-      </c>
-      <c r="O123" s="81">
-        <v>-5.5619169979571802E-2</v>
-      </c>
-      <c r="P123" s="81">
-        <v>0.36719089112522002</v>
-      </c>
-      <c r="Q123" s="81">
-        <v>0.308848626330535</v>
-      </c>
-      <c r="R123" s="81">
-        <v>0.11748042164024999</v>
-      </c>
-      <c r="S123" s="82">
-        <v>0.14822179182482301</v>
+      <c r="E123" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="G123" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H123" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I123" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J123" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="K123" s="15">
+        <v>9.9299999999999996E-4</v>
+      </c>
+      <c r="L123" s="16">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="M123" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N123" s="15">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="O123" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P123" s="15">
+        <v>4.6796999999999998E-2</v>
+      </c>
+      <c r="Q123" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R123" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S123" s="16">
+        <v>1.6E-2</v>
       </c>
     </row>
     <row r="124" spans="5:19">
       <c r="E124" s="45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F124" s="83">
-        <v>0.105993129702547</v>
-      </c>
-      <c r="G124" s="84">
-        <v>3.23762273213794E-3</v>
-      </c>
-      <c r="H124" s="84">
-        <v>0.19352969658929201</v>
-      </c>
-      <c r="I124" s="84"/>
-      <c r="J124" s="84"/>
-      <c r="K124" s="84">
-        <v>5.6159035224220402E-2</v>
-      </c>
-      <c r="L124" s="85">
-        <v>-4.8860835479998102E-2</v>
-      </c>
-      <c r="M124" s="83">
-        <v>5.3262323374033103E-2</v>
-      </c>
-      <c r="N124" s="84">
-        <v>0.15463285289956599</v>
-      </c>
-      <c r="O124" s="84">
-        <v>-3.08709378471714E-2</v>
-      </c>
-      <c r="P124" s="84">
-        <v>0.39061055793615201</v>
-      </c>
-      <c r="Q124" s="84">
-        <v>0.25572286157304402</v>
-      </c>
-      <c r="R124" s="84">
-        <v>8.3214842135471201E-2</v>
-      </c>
-      <c r="S124" s="85">
-        <v>0.143943452105049</v>
+        <v>10</v>
+      </c>
+      <c r="F124" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G124" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H124" s="15">
+        <v>3.9799999999999899E-4</v>
+      </c>
+      <c r="I124" s="226">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J124" s="219"/>
+      <c r="K124" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="L124" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M124" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N124" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O124" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P124" s="219"/>
+      <c r="Q124" s="219"/>
+      <c r="R124" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S124" s="16">
+        <v>1.0000000000000001E-5</v>
       </c>
     </row>
     <row r="125" spans="5:19">
       <c r="E125" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F125" s="83">
-        <v>-4.8967910079383802E-2</v>
-      </c>
-      <c r="G125" s="84">
-        <v>-9.5762791038125697E-2</v>
-      </c>
-      <c r="H125" s="84">
-        <v>5.8688261932670099E-2</v>
-      </c>
-      <c r="I125" s="84">
-        <v>-0.34296259052245398</v>
-      </c>
-      <c r="J125" s="84">
-        <v>-0.30051994156900402</v>
-      </c>
-      <c r="K125" s="84">
-        <v>-5.2145470276465801E-2</v>
-      </c>
-      <c r="L125" s="85">
-        <v>-1.47383467266508E-2</v>
-      </c>
-      <c r="M125" s="83">
-        <v>-4.4926539793208098E-2</v>
-      </c>
-      <c r="N125" s="84">
-        <v>3.55764793665388E-2</v>
-      </c>
-      <c r="O125" s="84">
-        <v>-8.0686439156473194E-2</v>
-      </c>
-      <c r="P125" s="84">
-        <v>0.38756219702384898</v>
-      </c>
-      <c r="Q125" s="84">
-        <v>0.16215221256593201</v>
-      </c>
-      <c r="R125" s="84">
-        <v>0.20848208718219999</v>
-      </c>
-      <c r="S125" s="85">
-        <v>2.2248427672955901E-2</v>
+        <v>11</v>
+      </c>
+      <c r="F125" s="14">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="G125" s="15">
+        <v>3.4849999999999998E-3</v>
+      </c>
+      <c r="H125" s="15">
+        <v>0.123</v>
+      </c>
+      <c r="I125" s="15">
+        <v>1.098E-3</v>
+      </c>
+      <c r="J125" s="219"/>
+      <c r="K125" s="219">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="L125" s="221"/>
+      <c r="M125" s="14">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="N125" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="O125" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P125" s="219">
+        <v>0.35169699999999998</v>
+      </c>
+      <c r="Q125" s="219"/>
+      <c r="R125" s="219">
+        <v>1E-3</v>
+      </c>
+      <c r="S125" s="221">
+        <v>6.4000000000000001E-2</v>
       </c>
     </row>
     <row r="126" spans="5:19">
       <c r="E126" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" s="14">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G126" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H126" s="15">
+        <v>2.3860000000000001E-3</v>
+      </c>
+      <c r="I126" s="15">
+        <v>9.6000000000000002E-4</v>
+      </c>
+      <c r="J126" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="K126" s="219">
+        <v>0.84340000000000004</v>
+      </c>
+      <c r="L126" s="221">
+        <v>0.501</v>
+      </c>
+      <c r="M126" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N126" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O126" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P126" s="219">
+        <v>2.35E-2</v>
+      </c>
+      <c r="Q126" s="219"/>
+      <c r="R126" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S126" s="221"/>
+    </row>
+    <row r="127" spans="5:19">
+      <c r="E127" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="223"/>
+      <c r="G127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K127" s="220">
+        <v>1E-3</v>
+      </c>
+      <c r="L127" s="222"/>
+      <c r="M127" s="17">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O127" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P127" s="220">
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q127" s="220"/>
+      <c r="R127" s="220"/>
+      <c r="S127" s="222"/>
+    </row>
+    <row r="129" spans="5:19">
+      <c r="E129" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F129" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G129" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H129" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I129" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J129" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K129" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L129" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M129" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N129" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O129" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P129" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="F126" s="83">
+      <c r="Q129" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R129" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S129" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="5:19">
+      <c r="E130" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F130" s="29">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H130" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J130" s="31">
+        <v>1.9E-3</v>
+      </c>
+      <c r="K130" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="L130" s="33">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M130" s="29">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O130" s="31">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="P130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R130" s="31">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S130" s="33">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="131" spans="5:19">
+      <c r="E131" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F131" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G131" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H131" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I131" s="30">
+        <v>9.6999999999999897E-4</v>
+      </c>
+      <c r="J131" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="K131" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="L131" s="34">
+        <v>5.73999999999994E-4</v>
+      </c>
+      <c r="M131" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N131" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O131" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P131" s="215"/>
+      <c r="Q131" s="215"/>
+      <c r="R131" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S131" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="132" spans="5:19">
+      <c r="E132" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F132" s="32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G132" s="30">
+        <v>7.8890000000000002E-2</v>
+      </c>
+      <c r="H132" s="30">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="I132" s="30">
+        <v>5.0478999999999899E-2</v>
+      </c>
+      <c r="J132" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K132" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="L132" s="34">
+        <v>0.32219999999999999</v>
+      </c>
+      <c r="M132" s="32">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="N132" s="30">
+        <v>7.2999999999999801E-3</v>
+      </c>
+      <c r="O132" s="30">
+        <v>0.1739</v>
+      </c>
+      <c r="P132" s="30">
+        <v>1.0999999999999901E-3</v>
+      </c>
+      <c r="Q132" s="30">
+        <v>1.6000000000000001E-3</v>
+      </c>
+      <c r="R132" s="30">
+        <v>0.24149999999999899</v>
+      </c>
+      <c r="S132" s="34">
+        <v>6.9000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="133" spans="5:19">
+      <c r="E133" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F133" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G133" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H133" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I133" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J133" s="215"/>
+      <c r="K133" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L133" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M133" s="32">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N133" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O133" s="30">
+        <v>5.6799999999999899E-2</v>
+      </c>
+      <c r="P133" s="225">
+        <v>9.8899999999999899E-4</v>
+      </c>
+      <c r="Q133" s="215"/>
+      <c r="R133" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="S133" s="34">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="134" spans="5:19">
+      <c r="E134" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="32">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="G134" s="30">
+        <v>0.25509100000000001</v>
+      </c>
+      <c r="H134" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I134" s="215">
+        <v>0.10059999999999999</v>
+      </c>
+      <c r="J134" s="215"/>
+      <c r="K134" s="215"/>
+      <c r="L134" s="216"/>
+      <c r="M134" s="32">
+        <v>0.2792</v>
+      </c>
+      <c r="N134" s="30">
+        <v>0.17979999999999999</v>
+      </c>
+      <c r="O134" s="30">
+        <v>0.56720000000000004</v>
+      </c>
+      <c r="P134" s="30">
+        <v>3.0793999999999901E-2</v>
+      </c>
+      <c r="Q134" s="215">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R134" s="215">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="S134" s="216"/>
+    </row>
+    <row r="135" spans="5:19">
+      <c r="E135" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="F135" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="G135" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="H135" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="I135" s="215">
+        <v>0.17199999999999999</v>
+      </c>
+      <c r="J135" s="215"/>
+      <c r="K135" s="215">
+        <v>2E-3</v>
+      </c>
+      <c r="L135" s="216"/>
+      <c r="M135" s="32">
+        <v>0.144199999999999</v>
+      </c>
+      <c r="N135" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="O135" s="30">
+        <v>8.0599999999999894E-2</v>
+      </c>
+      <c r="P135" s="30">
+        <v>1.9529999999999899E-3</v>
+      </c>
+      <c r="Q135" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="R135" s="215"/>
+      <c r="S135" s="216"/>
+    </row>
+    <row r="136" spans="5:19">
+      <c r="E136" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F136" s="37">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G136" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H136" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="I136" s="217"/>
+      <c r="J136" s="217">
+        <v>1E-3</v>
+      </c>
+      <c r="K136" s="217"/>
+      <c r="L136" s="218">
+        <v>1E-3</v>
+      </c>
+      <c r="M136" s="224"/>
+      <c r="N136" s="36">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O136" s="36">
+        <v>0.13339999999999899</v>
+      </c>
+      <c r="P136" s="36">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="Q136" s="36">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="R136" s="217">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S136" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="137" spans="5:19">
+      <c r="E137" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F137" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G137" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H137" s="12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I137" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J137" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="K137" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L137" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M137" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N137" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O137" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="P137" s="12">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q137" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="R137" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="S137" s="13">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="138" spans="5:19">
+      <c r="E138" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F138" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G138" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H138" s="15">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="I138" s="219"/>
+      <c r="J138" s="219"/>
+      <c r="K138" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="L138" s="16">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M138" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N138" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O138" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P138" s="15">
+        <v>9.6000000000000002E-4</v>
+      </c>
+      <c r="Q138" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="R138" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="S138" s="16">
+        <v>9.3000000000000005E-4</v>
+      </c>
+    </row>
+    <row r="139" spans="5:19">
+      <c r="E139" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="14">
+        <v>0.112897</v>
+      </c>
+      <c r="G139" s="15">
+        <v>2.55199999999999E-3</v>
+      </c>
+      <c r="H139" s="15">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="I139" s="15">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="J139" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="K139" s="15">
+        <v>1.9E-3</v>
+      </c>
+      <c r="L139" s="16">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="M139" s="14">
+        <v>1.98E-3</v>
+      </c>
+      <c r="N139" s="15">
+        <v>3.5699999999999898E-2</v>
+      </c>
+      <c r="O139" s="15">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="P139" s="15">
+        <v>0.126</v>
+      </c>
+      <c r="Q139" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="R139" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S139" s="16">
+        <v>2.35E-2</v>
+      </c>
+    </row>
+    <row r="140" spans="5:19">
+      <c r="E140" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G140" s="15">
+        <v>1.91999999999989E-4</v>
+      </c>
+      <c r="H140" s="15">
+        <v>1.9839999999999901E-3</v>
+      </c>
+      <c r="I140" s="226">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J140" s="219"/>
+      <c r="K140" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="L140" s="16">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="M140" s="14">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N140" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O140" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P140" s="219"/>
+      <c r="Q140" s="219"/>
+      <c r="R140" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="S140" s="16">
+        <v>1.0599999999999701E-4</v>
+      </c>
+    </row>
+    <row r="141" spans="5:19">
+      <c r="E141" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="14">
+        <v>0.29698999999999998</v>
+      </c>
+      <c r="G141" s="15">
+        <v>0.196995</v>
+      </c>
+      <c r="H141" s="15">
+        <v>0.1953</v>
+      </c>
+      <c r="I141" s="15">
+        <v>0.13669999999999899</v>
+      </c>
+      <c r="J141" s="219"/>
+      <c r="K141" s="219">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="L141" s="221"/>
+      <c r="M141" s="14">
+        <v>0.1966</v>
+      </c>
+      <c r="N141" s="15">
+        <v>0.215</v>
+      </c>
+      <c r="O141" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P141" s="219">
+        <v>0.67820000000000003</v>
+      </c>
+      <c r="Q141" s="219"/>
+      <c r="R141" s="219">
+        <v>1E-3</v>
+      </c>
+      <c r="S141" s="221">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="142" spans="5:19">
+      <c r="E142" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F142" s="14">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="G142" s="15">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="H142" s="15">
+        <v>1.5699999999999902E-2</v>
+      </c>
+      <c r="I142" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="J142" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="K142" s="219">
+        <v>1.73219999999999</v>
+      </c>
+      <c r="L142" s="221">
+        <v>0.501</v>
+      </c>
+      <c r="M142" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="N142" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="O142" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="P142" s="219">
+        <v>0.2525</v>
+      </c>
+      <c r="Q142" s="219"/>
+      <c r="R142" s="219">
+        <v>1.005E-3</v>
+      </c>
+      <c r="S142" s="221"/>
+    </row>
+    <row r="143" spans="5:19">
+      <c r="E143" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F143" s="223"/>
+      <c r="G143" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H143" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="I143" s="18">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="J143" s="18">
+        <v>2.0599999999999899E-4</v>
+      </c>
+      <c r="K143" s="220">
+        <v>1E-3</v>
+      </c>
+      <c r="L143" s="222"/>
+      <c r="M143" s="17">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N143" s="18">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O143" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="P143" s="220">
+        <v>1.5999999999999901E-3</v>
+      </c>
+      <c r="Q143" s="220"/>
+      <c r="R143" s="220"/>
+      <c r="S143" s="222"/>
+    </row>
+    <row r="145" spans="5:19">
+      <c r="E145" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F145" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G145" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H145" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I145" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J145" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K145" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L145" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M145" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N145" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O145" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P145" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q145" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R145" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S145" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="5:19">
+      <c r="E146" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F146" s="29">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G146" s="31">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="H146" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="I146" s="31">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="J146" s="31">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K146" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="L146" s="33">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="M146" s="29">
+        <v>1E-3</v>
+      </c>
+      <c r="N146" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="O146" s="31">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="P146" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="Q146" s="31">
+        <v>1.99E-3</v>
+      </c>
+      <c r="R146" s="31">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="S146" s="33">
+        <v>9.7999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="147" spans="5:19">
+      <c r="E147" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F147" s="32">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="G147" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="H147" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I147" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="J147" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K147" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="L147" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="M147" s="32">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="N147" s="30">
+        <v>9.5E-4</v>
+      </c>
+      <c r="O147" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="P147" s="215"/>
+      <c r="Q147" s="215"/>
+      <c r="R147" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="S147" s="34">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="148" spans="5:19">
+      <c r="E148" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F148" s="32">
+        <v>0.189</v>
+      </c>
+      <c r="G148" s="30">
+        <v>0.27549000000000001</v>
+      </c>
+      <c r="H148" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I148" s="30">
+        <v>0.17</v>
+      </c>
+      <c r="J148" s="30">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K148" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="L148" s="34">
+        <v>0.46949999999999997</v>
+      </c>
+      <c r="M148" s="32">
+        <v>0.40348000000000001</v>
+      </c>
+      <c r="N148" s="30">
+        <v>0.161995</v>
+      </c>
+      <c r="O148" s="30">
+        <v>0.40649999999999997</v>
+      </c>
+      <c r="P148" s="30">
+        <v>5.9950000000000003E-3</v>
+      </c>
+      <c r="Q148" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="R148" s="30">
+        <v>0.51249999999999996</v>
+      </c>
+      <c r="S148" s="34">
+        <v>0.12848999999999999</v>
+      </c>
+    </row>
+    <row r="149" spans="5:19">
+      <c r="E149" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F149" s="32">
+        <v>1E-3</v>
+      </c>
+      <c r="G149" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="H149" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I149" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J149" s="215"/>
+      <c r="K149" s="30">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="L149" s="34">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="M149" s="32">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="N149" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="O149" s="30">
+        <v>9.4E-2</v>
+      </c>
+      <c r="P149" s="225">
+        <v>1E-3</v>
+      </c>
+      <c r="Q149" s="215"/>
+      <c r="R149" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="S149" s="34">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="150" spans="5:19">
+      <c r="E150" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F150" s="32">
+        <v>0.54400000000000004</v>
+      </c>
+      <c r="G150" s="30">
+        <v>0.6905</v>
+      </c>
+      <c r="H150" s="30">
+        <v>1.4E-2</v>
+      </c>
+      <c r="I150" s="215">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="J150" s="215"/>
+      <c r="K150" s="215"/>
+      <c r="L150" s="216"/>
+      <c r="M150" s="32">
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="N150" s="30">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="O150" s="30">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="P150" s="30">
+        <v>0.23350000000000001</v>
+      </c>
+      <c r="Q150" s="215">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R150" s="215">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="S150" s="216"/>
+    </row>
+    <row r="151" spans="5:19">
+      <c r="E151" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="F151" s="32">
+        <v>2E-3</v>
+      </c>
+      <c r="G151" s="30">
+        <v>0.112985</v>
+      </c>
+      <c r="H151" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="I151" s="215">
+        <v>0.20649999999999999</v>
+      </c>
+      <c r="J151" s="215"/>
+      <c r="K151" s="215">
+        <v>2E-3</v>
+      </c>
+      <c r="L151" s="216"/>
+      <c r="M151" s="32">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="N151" s="30">
+        <v>1.5994999999999999E-2</v>
+      </c>
+      <c r="O151" s="30">
+        <v>0.221</v>
+      </c>
+      <c r="P151" s="30">
+        <v>2.97E-3</v>
+      </c>
+      <c r="Q151" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="R151" s="215"/>
+      <c r="S151" s="216"/>
+    </row>
+    <row r="152" spans="5:19">
+      <c r="E152" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F152" s="37">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="G152" s="36">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="H152" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="I152" s="217"/>
+      <c r="J152" s="217">
+        <v>1E-3</v>
+      </c>
+      <c r="K152" s="217"/>
+      <c r="L152" s="218">
+        <v>1E-3</v>
+      </c>
+      <c r="M152" s="224"/>
+      <c r="N152" s="36">
+        <v>9.7000000000000005E-4</v>
+      </c>
+      <c r="O152" s="36">
+        <v>0.34899999999999998</v>
+      </c>
+      <c r="P152" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="Q152" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="R152" s="217">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S152" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="153" spans="5:19">
+      <c r="E153" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F153" s="11">
+        <v>1E-3</v>
+      </c>
+      <c r="G153" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="H153" s="12">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="I153" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="J153" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="K153" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="L153" s="13">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="M153" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N153" s="12">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="O153" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="P153" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="Q153" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="R153" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="S153" s="13">
+        <v>9.7999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="154" spans="5:19">
+      <c r="E154" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F154" s="14">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="G154" s="15">
+        <v>9.5E-4</v>
+      </c>
+      <c r="H154" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="I154" s="219"/>
+      <c r="J154" s="219"/>
+      <c r="K154" s="15">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="L154" s="16">
+        <v>9.4499999999999998E-4</v>
+      </c>
+      <c r="M154" s="14">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="N154" s="15">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="O154" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P154" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="Q154" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R154" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="S154" s="16">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="155" spans="5:19">
+      <c r="E155" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="14">
+        <v>0.36</v>
+      </c>
+      <c r="G155" s="15">
+        <v>0.12</v>
+      </c>
+      <c r="H155" s="15">
+        <v>0.499</v>
+      </c>
+      <c r="I155" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="J155" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="K155" s="15">
+        <v>0.1065</v>
+      </c>
+      <c r="L155" s="16">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="M155" s="14">
+        <v>0.129995</v>
+      </c>
+      <c r="N155" s="15">
+        <v>0.2215</v>
+      </c>
+      <c r="O155" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P155" s="15">
+        <v>0.312</v>
+      </c>
+      <c r="Q155" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="R155" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="S155" s="16">
+        <v>2.9499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="5:19">
+      <c r="E156" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" s="14">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="G156" s="15">
+        <v>9.9799999999999993E-3</v>
+      </c>
+      <c r="H156" s="15">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I156" s="226">
+        <v>1E-3</v>
+      </c>
+      <c r="J156" s="219"/>
+      <c r="K156" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="L156" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="M156" s="14">
+        <v>9.9500000000000001E-4</v>
+      </c>
+      <c r="N156" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="O156" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P156" s="219"/>
+      <c r="Q156" s="219"/>
+      <c r="R156" s="15">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="S156" s="16">
+        <v>9.8999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="157" spans="5:19">
+      <c r="E157" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="14">
+        <v>0.94</v>
+      </c>
+      <c r="G157" s="15">
+        <v>0.44499499999999997</v>
+      </c>
+      <c r="H157" s="15">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I157" s="15">
+        <v>0.47649999999999998</v>
+      </c>
+      <c r="J157" s="219"/>
+      <c r="K157" s="219">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="L157" s="221"/>
+      <c r="M157" s="14">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="N157" s="15">
+        <v>0.64600000000000002</v>
+      </c>
+      <c r="O157" s="15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="P157" s="219">
+        <v>1.7504999999999999</v>
+      </c>
+      <c r="Q157" s="219"/>
+      <c r="R157" s="219">
+        <v>1E-3</v>
+      </c>
+      <c r="S157" s="221">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="5:19">
+      <c r="E158" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="14">
+        <v>0.48099999999999998</v>
+      </c>
+      <c r="G158" s="15">
+        <v>4.9699999999999996E-3</v>
+      </c>
+      <c r="H158" s="15">
+        <v>0.29599999999999999</v>
+      </c>
+      <c r="I158" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="J158" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="K158" s="219">
+        <v>2.621</v>
+      </c>
+      <c r="L158" s="221">
+        <v>0.501</v>
+      </c>
+      <c r="M158" s="14">
+        <v>3.9899999999999996E-3</v>
+      </c>
+      <c r="N158" s="15">
+        <v>2.35E-2</v>
+      </c>
+      <c r="O158" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="P158" s="219">
+        <v>0.67349999999999999</v>
+      </c>
+      <c r="Q158" s="219"/>
+      <c r="R158" s="219">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="S158" s="221"/>
+    </row>
+    <row r="159" spans="5:19">
+      <c r="E159" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F159" s="223"/>
+      <c r="G159" s="18">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="H159" s="18">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="I159" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="J159" s="18">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="K159" s="220">
+        <v>1E-3</v>
+      </c>
+      <c r="L159" s="222"/>
+      <c r="M159" s="17">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="N159" s="18">
+        <v>9.8499999999999998E-4</v>
+      </c>
+      <c r="O159" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="P159" s="220">
+        <v>2E-3</v>
+      </c>
+      <c r="Q159" s="220"/>
+      <c r="R159" s="220"/>
+      <c r="S159" s="222"/>
+    </row>
+    <row r="161" spans="5:19">
+      <c r="E161" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F161" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G161" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H161" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I161" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J161" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K161" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L161" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M161" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N161" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O161" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P161" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q161" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R161" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S161" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162" spans="5:19">
+      <c r="E162" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F162" s="29">
+        <v>9.3000000000000005E-4</v>
+      </c>
+      <c r="G162" s="31">
+        <v>2.99E-3</v>
+      </c>
+      <c r="H162" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="I162" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="J162" s="31">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K162" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="L162" s="33">
+        <v>1E-3</v>
+      </c>
+      <c r="M162" s="29">
+        <v>0.20729699999999901</v>
+      </c>
+      <c r="N162" s="31">
+        <v>7.8999999999999904E-2</v>
+      </c>
+      <c r="O162" s="31">
+        <v>0.42559999999999998</v>
+      </c>
+      <c r="P162" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="Q162" s="31">
+        <v>2E-3</v>
+      </c>
+      <c r="R162" s="31">
+        <v>1E-3</v>
+      </c>
+      <c r="S162" s="33">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="5:19">
+      <c r="E163" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F163" s="32">
+        <v>1.99E-3</v>
+      </c>
+      <c r="G163" s="30">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="H163" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="I163" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="J163" s="30">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K163" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="L163" s="34">
+        <v>2E-3</v>
+      </c>
+      <c r="M163" s="32">
+        <v>1.98E-3</v>
+      </c>
+      <c r="N163" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="O163" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="P163" s="215"/>
+      <c r="Q163" s="215"/>
+      <c r="R163" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="S163" s="34">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="5:19">
+      <c r="E164" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F164" s="32">
+        <v>0.73319999999999896</v>
+      </c>
+      <c r="G164" s="30">
+        <v>0.863679999999999</v>
+      </c>
+      <c r="H164" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I164" s="30">
+        <v>0.73008799999999896</v>
+      </c>
+      <c r="J164" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="K164" s="30">
+        <v>9.4767999999999894E-2</v>
+      </c>
+      <c r="L164" s="34">
+        <v>0.6069</v>
+      </c>
+      <c r="M164" s="32">
+        <v>0.95050000000000001</v>
+      </c>
+      <c r="N164" s="30">
+        <v>0.65869999999999995</v>
+      </c>
+      <c r="O164" s="30">
+        <v>0.88819999999999999</v>
+      </c>
+      <c r="P164" s="30">
+        <v>0.181399</v>
+      </c>
+      <c r="Q164" s="30">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R164" s="30">
+        <v>0.57509999999999994</v>
+      </c>
+      <c r="S164" s="34">
+        <v>0.26799999999999902</v>
+      </c>
+    </row>
+    <row r="165" spans="5:19">
+      <c r="E165" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F165" s="32">
+        <v>2.4494999999999999E-2</v>
+      </c>
+      <c r="G165" s="30">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="H165" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="I165" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J165" s="215"/>
+      <c r="K165" s="30">
+        <v>1E-3</v>
+      </c>
+      <c r="L165" s="34">
+        <v>1E-3</v>
+      </c>
+      <c r="M165" s="32">
+        <v>5.2591999999999903E-2</v>
+      </c>
+      <c r="N165" s="30">
+        <v>0.16539999999999999</v>
+      </c>
+      <c r="O165" s="30">
+        <v>0.45679999999999998</v>
+      </c>
+      <c r="P165" s="225">
+        <v>1.09799999999999E-3</v>
+      </c>
+      <c r="Q165" s="215"/>
+      <c r="R165" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="S165" s="34">
+        <v>2.2499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="5:19">
+      <c r="E166" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F166" s="32">
+        <v>1.3914</v>
+      </c>
+      <c r="G166" s="30">
+        <v>1.3677999999999999</v>
+      </c>
+      <c r="H166" s="30">
+        <v>0.55979999999999897</v>
+      </c>
+      <c r="I166" s="215">
+        <v>0.60059999999999902</v>
+      </c>
+      <c r="J166" s="215"/>
+      <c r="K166" s="215"/>
+      <c r="L166" s="216"/>
+      <c r="M166" s="32">
+        <v>1.4383999999999999</v>
+      </c>
+      <c r="N166" s="30">
+        <v>1.09109999999999</v>
+      </c>
+      <c r="O166" s="30">
+        <v>2.0283999999999902</v>
+      </c>
+      <c r="P166" s="30">
+        <v>0.60069999999999901</v>
+      </c>
+      <c r="Q166" s="215">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R166" s="215">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="S166" s="216"/>
+    </row>
+    <row r="167" spans="5:19">
+      <c r="E167" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="F167" s="32">
+        <v>0.17699000000000001</v>
+      </c>
+      <c r="G167" s="30">
+        <v>0.42849999999999999</v>
+      </c>
+      <c r="H167" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="I167" s="215">
+        <v>1.05459999999999</v>
+      </c>
+      <c r="J167" s="215"/>
+      <c r="K167" s="215">
+        <v>2E-3</v>
+      </c>
+      <c r="L167" s="216"/>
+      <c r="M167" s="32">
+        <v>0.79419999999999902</v>
+      </c>
+      <c r="N167" s="30">
+        <v>0.163997</v>
+      </c>
+      <c r="O167" s="30">
+        <v>1.58459999999999</v>
+      </c>
+      <c r="P167" s="30">
+        <v>0.128299999999999</v>
+      </c>
+      <c r="Q167" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R167" s="215"/>
+      <c r="S167" s="216"/>
+    </row>
+    <row r="168" spans="5:19">
+      <c r="E168" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F168" s="37">
+        <v>1E-3</v>
+      </c>
+      <c r="G168" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="H168" s="36">
+        <v>2E-3</v>
+      </c>
+      <c r="I168" s="217"/>
+      <c r="J168" s="217">
+        <v>1E-3</v>
+      </c>
+      <c r="K168" s="217"/>
+      <c r="L168" s="218">
+        <v>1E-3</v>
+      </c>
+      <c r="M168" s="224"/>
+      <c r="N168" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="O168" s="36">
+        <v>0.90679999999999905</v>
+      </c>
+      <c r="P168" s="36">
+        <v>1.99E-3</v>
+      </c>
+      <c r="Q168" s="36">
+        <v>1.99E-3</v>
+      </c>
+      <c r="R168" s="217">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S168" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="169" spans="5:19">
+      <c r="E169" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F169" s="11">
+        <v>0.14829999999999999</v>
+      </c>
+      <c r="G169" s="12">
+        <v>4.5987999999999897E-2</v>
+      </c>
+      <c r="H169" s="12">
+        <v>0.48119999999999902</v>
+      </c>
+      <c r="I169" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="J169" s="12">
+        <v>2.9970000000000001E-3</v>
+      </c>
+      <c r="K169" s="12">
+        <v>1E-3</v>
+      </c>
+      <c r="L169" s="13">
+        <v>1E-3</v>
+      </c>
+      <c r="M169" s="11">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="N169" s="12">
+        <v>2.98E-3</v>
+      </c>
+      <c r="O169" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="P169" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="Q169" s="12">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R169" s="12">
+        <v>2E-3</v>
+      </c>
+      <c r="S169" s="13">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="5:19">
+      <c r="E170" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F170" s="14">
+        <v>2E-3</v>
+      </c>
+      <c r="G170" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="H170" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I170" s="219"/>
+      <c r="J170" s="219"/>
+      <c r="K170" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="L170" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="M170" s="14">
+        <v>1E-3</v>
+      </c>
+      <c r="N170" s="15">
+        <v>9.7999999999999997E-4</v>
+      </c>
+      <c r="O170" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="P170" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="Q170" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="R170" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="S170" s="16">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="171" spans="5:19">
+      <c r="E171" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="14">
+        <v>1.0679810000000001</v>
+      </c>
+      <c r="G171" s="15">
+        <v>0.38500000000000001</v>
+      </c>
+      <c r="H171" s="15">
+        <v>1.2529999999999999</v>
+      </c>
+      <c r="I171" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="J171" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="K171" s="15">
+        <v>0.17419999999999999</v>
+      </c>
+      <c r="L171" s="16">
+        <v>0.1308</v>
+      </c>
+      <c r="M171" s="14">
+        <v>0.53709999999999902</v>
+      </c>
+      <c r="N171" s="15">
+        <v>0.75089999999999901</v>
+      </c>
+      <c r="O171" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="P171" s="15">
+        <v>0.72319999999999995</v>
+      </c>
+      <c r="Q171" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="R171" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="S171" s="16">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="172" spans="5:19">
+      <c r="E172" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" s="14">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G172" s="15">
+        <v>0.15879199999999899</v>
+      </c>
+      <c r="H172" s="15">
+        <v>0.134799999999999</v>
+      </c>
+      <c r="I172" s="226">
+        <v>1E-3</v>
+      </c>
+      <c r="J172" s="219"/>
+      <c r="K172" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="L172" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="M172" s="14">
+        <v>1.30999999999999E-2</v>
+      </c>
+      <c r="N172" s="15">
+        <v>3.4999999999999802E-2</v>
+      </c>
+      <c r="O172" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="P172" s="219"/>
+      <c r="Q172" s="219"/>
+      <c r="R172" s="15">
+        <v>1E-3</v>
+      </c>
+      <c r="S172" s="16">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="5:19">
+      <c r="E173" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="14">
+        <v>1.665</v>
+      </c>
+      <c r="G173" s="15">
+        <v>1.1014999999999999</v>
+      </c>
+      <c r="H173" s="15">
+        <v>1.3711</v>
+      </c>
+      <c r="I173" s="15">
+        <v>0.93019999999999903</v>
+      </c>
+      <c r="J173" s="219"/>
+      <c r="K173" s="219">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="L173" s="221"/>
+      <c r="M173" s="14">
+        <v>1.2696000000000001</v>
+      </c>
+      <c r="N173" s="15">
+        <v>1.3380000000000001</v>
+      </c>
+      <c r="O173" s="15">
+        <v>0.753</v>
+      </c>
+      <c r="P173" s="219">
+        <v>2.3458000000000001</v>
+      </c>
+      <c r="Q173" s="219"/>
+      <c r="R173" s="219">
+        <v>1E-3</v>
+      </c>
+      <c r="S173" s="221">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="5:19">
+      <c r="E174" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="14">
+        <v>1.24799999999999</v>
+      </c>
+      <c r="G174" s="15">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="H174" s="15">
+        <v>0.56689999999999996</v>
+      </c>
+      <c r="I174" s="15">
+        <v>3.9967999999999997E-2</v>
+      </c>
+      <c r="J174" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="K174" s="219">
+        <v>3.5097999999999998</v>
+      </c>
+      <c r="L174" s="221">
+        <v>0.501</v>
+      </c>
+      <c r="M174" s="14">
+        <v>0.18679399999999899</v>
+      </c>
+      <c r="N174" s="15">
+        <v>0.283390999999999</v>
+      </c>
+      <c r="O174" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="P174" s="219">
+        <v>0.9345</v>
+      </c>
+      <c r="Q174" s="219"/>
+      <c r="R174" s="219">
+        <v>1.2E-2</v>
+      </c>
+      <c r="S174" s="221"/>
+    </row>
+    <row r="175" spans="5:19">
+      <c r="E175" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="223"/>
+      <c r="G175" s="18">
+        <v>1.9779999999999902E-3</v>
+      </c>
+      <c r="H175" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="I175" s="18">
+        <v>2E-3</v>
+      </c>
+      <c r="J175" s="18">
+        <v>9.8999999999999999E-4</v>
+      </c>
+      <c r="K175" s="220">
+        <v>1E-3</v>
+      </c>
+      <c r="L175" s="222"/>
+      <c r="M175" s="17">
+        <v>1E-3</v>
+      </c>
+      <c r="N175" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="O175" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="P175" s="220">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="Q175" s="220"/>
+      <c r="R175" s="220"/>
+      <c r="S175" s="222"/>
+    </row>
+    <row r="177" spans="5:19">
+      <c r="E177" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F177" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G177" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H177" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I177" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J177" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K177" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L177" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M177" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N177" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O177" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P177" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q177" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R177" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S177" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="5:19">
+      <c r="E178" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F178" s="29">
+        <v>2.97299999999999E-3</v>
+      </c>
+      <c r="G178" s="31">
+        <v>0.58150000000000102</v>
+      </c>
+      <c r="H178" s="31">
+        <v>0.51649999999999996</v>
+      </c>
+      <c r="I178" s="31">
+        <v>0.46119300000000002</v>
+      </c>
+      <c r="J178" s="31">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K178" s="31">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L178" s="33">
+        <v>2E-3</v>
+      </c>
+      <c r="M178" s="29">
+        <v>1.4994999999999901</v>
+      </c>
+      <c r="N178" s="31">
+        <v>0.83758200000000005</v>
+      </c>
+      <c r="O178" s="31">
+        <v>2.2555999999999998</v>
+      </c>
+      <c r="P178" s="31">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="Q178" s="31">
+        <v>3.0999999999999999E-3</v>
+      </c>
+      <c r="R178" s="31">
+        <v>3.9919999999999999E-3</v>
+      </c>
+      <c r="S178" s="33">
+        <v>5.39399999999997E-3</v>
+      </c>
+    </row>
+    <row r="179" spans="5:19">
+      <c r="E179" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F179" s="32">
+        <v>0.30099300000000001</v>
+      </c>
+      <c r="G179" s="30">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="H179" s="30">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="I179" s="30">
+        <v>5.5482000000000101E-2</v>
+      </c>
+      <c r="J179" s="30">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="K179" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L179" s="34">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="M179" s="32">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="N179" s="30">
+        <v>0.37018799999999902</v>
+      </c>
+      <c r="O179" s="30">
+        <v>0.58479999999999999</v>
+      </c>
+      <c r="P179" s="215"/>
+      <c r="Q179" s="215"/>
+      <c r="R179" s="30">
+        <v>2E-3</v>
+      </c>
+      <c r="S179" s="34">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="180" spans="5:19">
+      <c r="E180" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F180" s="32">
+        <v>2.4691999999999998</v>
+      </c>
+      <c r="G180" s="30">
+        <v>2.8259970000000001</v>
+      </c>
+      <c r="H180" s="30">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="I180" s="30">
+        <v>1.2997999999999901</v>
+      </c>
+      <c r="J180" s="30">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="K180" s="30">
+        <v>0.42520000000000002</v>
+      </c>
+      <c r="L180" s="34">
+        <v>3.54578999999999</v>
+      </c>
+      <c r="M180" s="32">
+        <v>2.6915</v>
+      </c>
+      <c r="N180" s="30">
+        <v>2.60869999999999</v>
+      </c>
+      <c r="O180" s="30">
+        <v>3.0409000000000002</v>
+      </c>
+      <c r="P180" s="30">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="Q180" s="30">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="R180" s="30">
+        <v>0.95439999999999903</v>
+      </c>
+      <c r="S180" s="34">
+        <v>2.0708000000000002</v>
+      </c>
+    </row>
+    <row r="181" spans="5:19">
+      <c r="E181" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F181" s="32">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="G181" s="30">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="H181" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I181" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J181" s="215"/>
+      <c r="K181" s="30">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L181" s="34">
+        <v>0.2094</v>
+      </c>
+      <c r="M181" s="32">
+        <v>1.0052000000000001</v>
+      </c>
+      <c r="N181" s="30">
+        <v>1.0727979999999999</v>
+      </c>
+      <c r="O181" s="30">
+        <v>0.8196</v>
+      </c>
+      <c r="P181" s="225">
+        <v>2E-3</v>
+      </c>
+      <c r="Q181" s="215"/>
+      <c r="R181" s="30">
+        <v>0.233400000000001</v>
+      </c>
+      <c r="S181" s="34">
+        <v>0.24349999999999999</v>
+      </c>
+    </row>
+    <row r="182" spans="5:19">
+      <c r="E182" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="32">
+        <v>3.2012</v>
+      </c>
+      <c r="G182" s="30">
+        <v>3.2677999999999998</v>
+      </c>
+      <c r="H182" s="30">
+        <v>1.5133999999999901</v>
+      </c>
+      <c r="I182" s="215">
+        <v>1.2766</v>
+      </c>
+      <c r="J182" s="215"/>
+      <c r="K182" s="215"/>
+      <c r="L182" s="216"/>
+      <c r="M182" s="32">
+        <v>3.4268000000000001</v>
+      </c>
+      <c r="N182" s="30">
+        <v>2.6322999999999999</v>
+      </c>
+      <c r="O182" s="30">
+        <v>3.4384000000000001</v>
+      </c>
+      <c r="P182" s="30">
+        <v>2.0188999999999901</v>
+      </c>
+      <c r="Q182" s="215">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="R182" s="215">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="S182" s="216"/>
+    </row>
+    <row r="183" spans="5:19">
+      <c r="E183" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="F183" s="32">
+        <v>1.45</v>
+      </c>
+      <c r="G183" s="30">
+        <v>1.5988929999999999</v>
+      </c>
+      <c r="H183" s="30">
+        <v>0.22060000000000099</v>
+      </c>
+      <c r="I183" s="215">
+        <v>1.2284999999999999</v>
+      </c>
+      <c r="J183" s="215"/>
+      <c r="K183" s="215">
+        <v>2E-3</v>
+      </c>
+      <c r="L183" s="216"/>
+      <c r="M183" s="32">
+        <v>2.2185999999999999</v>
+      </c>
+      <c r="N183" s="30">
+        <v>0.84000000000000097</v>
+      </c>
+      <c r="O183" s="30">
+        <v>3.5764</v>
+      </c>
+      <c r="P183" s="30">
+        <v>0.50889899999999999</v>
+      </c>
+      <c r="Q183" s="30">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="R183" s="215"/>
+      <c r="S183" s="216"/>
+    </row>
+    <row r="184" spans="5:19">
+      <c r="E184" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F184" s="37">
+        <v>0.238591</v>
+      </c>
+      <c r="G184" s="36">
+        <v>0.108392</v>
+      </c>
+      <c r="H184" s="36">
+        <v>0.23229999999999901</v>
+      </c>
+      <c r="I184" s="217"/>
+      <c r="J184" s="217">
+        <v>1E-3</v>
+      </c>
+      <c r="K184" s="217"/>
+      <c r="L184" s="218">
+        <v>1E-3</v>
+      </c>
+      <c r="M184" s="224"/>
+      <c r="N184" s="36">
+        <v>0.28079599999999999</v>
+      </c>
+      <c r="O184" s="36">
+        <v>1.5711999999999999</v>
+      </c>
+      <c r="P184" s="36">
+        <v>7.0900000000000005E-2</v>
+      </c>
+      <c r="Q184" s="36">
+        <v>2.8E-3</v>
+      </c>
+      <c r="R184" s="217">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="S184" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+    <row r="185" spans="5:19">
+      <c r="E185" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F185" s="11">
+        <v>1.2961</v>
+      </c>
+      <c r="G185" s="12">
+        <v>0.74998400000000098</v>
+      </c>
+      <c r="H185" s="12">
+        <v>2.6318000000000001</v>
+      </c>
+      <c r="I185" s="12">
+        <v>0.112</v>
+      </c>
+      <c r="J185" s="12">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K185" s="12">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L185" s="13">
+        <v>2E-3</v>
+      </c>
+      <c r="M185" s="11">
+        <v>2E-3</v>
+      </c>
+      <c r="N185" s="12">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="O185" s="12">
+        <v>0.34439999999999998</v>
+      </c>
+      <c r="P185" s="12">
+        <v>0.56120000000000003</v>
+      </c>
+      <c r="Q185" s="12">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="R185" s="12">
+        <v>3.80000000000001E-3</v>
+      </c>
+      <c r="S185" s="13">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="186" spans="5:19">
+      <c r="E186" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F186" s="14">
+        <v>0.57519999999999905</v>
+      </c>
+      <c r="G186" s="15">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="H186" s="15">
+        <v>0.96620000000000295</v>
+      </c>
+      <c r="I186" s="219"/>
+      <c r="J186" s="219"/>
+      <c r="K186" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="L186" s="16">
+        <v>1.98E-3</v>
+      </c>
+      <c r="M186" s="14">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="N186" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="O186" s="15">
+        <v>4.5400000000000502E-2</v>
+      </c>
+      <c r="P186" s="15">
+        <v>0.129</v>
+      </c>
+      <c r="Q186" s="15">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="R186" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="S186" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="187" spans="5:19">
+      <c r="E187" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="14">
+        <v>3.3954</v>
+      </c>
+      <c r="G187" s="15">
+        <v>1.7342</v>
+      </c>
+      <c r="H187" s="15">
+        <v>2.2290000000000001</v>
+      </c>
+      <c r="I187" s="15">
+        <v>0.80150000000000099</v>
+      </c>
+      <c r="J187" s="15">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K187" s="15">
+        <v>0.74409999999999998</v>
+      </c>
+      <c r="L187" s="16">
+        <v>0.52299799999999996</v>
+      </c>
+      <c r="M187" s="14">
+        <v>2.1304999999999898</v>
+      </c>
+      <c r="N187" s="15">
+        <v>2.4209999999999998</v>
+      </c>
+      <c r="O187" s="15">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="P187" s="15">
+        <v>2.0428999999999999</v>
+      </c>
+      <c r="Q187" s="15">
+        <v>2E-3</v>
+      </c>
+      <c r="R187" s="15">
+        <v>7.2999999999999995E-2</v>
+      </c>
+      <c r="S187" s="16">
+        <v>8.7495000000000003E-2</v>
+      </c>
+    </row>
+    <row r="188" spans="5:19">
+      <c r="E188" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" s="14">
+        <v>1.123</v>
+      </c>
+      <c r="G188" s="15">
+        <v>1.1362000000000001</v>
+      </c>
+      <c r="H188" s="15">
+        <v>1.85</v>
+      </c>
+      <c r="I188" s="226">
+        <v>2.98E-3</v>
+      </c>
+      <c r="J188" s="219"/>
+      <c r="K188" s="15">
+        <v>3.8600000000000398E-2</v>
+      </c>
+      <c r="L188" s="16">
+        <v>0.23299999999999901</v>
+      </c>
+      <c r="M188" s="14">
+        <v>0.68549300000000002</v>
+      </c>
+      <c r="N188" s="15">
+        <v>0.76598999999999995</v>
+      </c>
+      <c r="O188" s="15">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="P188" s="219"/>
+      <c r="Q188" s="219"/>
+      <c r="R188" s="15">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="S188" s="16">
+        <v>0.65130000000000099</v>
+      </c>
+    </row>
+    <row r="189" spans="5:19">
+      <c r="E189" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" s="14">
+        <v>3.028</v>
+      </c>
+      <c r="G189" s="15">
+        <v>2.4419900000000001</v>
+      </c>
+      <c r="H189" s="15">
+        <v>4.0011999999999999</v>
+      </c>
+      <c r="I189" s="15">
+        <v>1.7937999999999901</v>
+      </c>
+      <c r="J189" s="219"/>
+      <c r="K189" s="219">
+        <v>0.40899999999999997</v>
+      </c>
+      <c r="L189" s="221"/>
+      <c r="M189" s="14">
+        <v>3.1679999999999899</v>
+      </c>
+      <c r="N189" s="15">
+        <v>3.1890000000000001</v>
+      </c>
+      <c r="O189" s="15">
+        <v>2.0419999999999998</v>
+      </c>
+      <c r="P189" s="219">
+        <v>3.5255969999999901</v>
+      </c>
+      <c r="Q189" s="219"/>
+      <c r="R189" s="219">
+        <v>1E-3</v>
+      </c>
+      <c r="S189" s="221">
+        <v>6.4000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="190" spans="5:19">
+      <c r="E190" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F190" s="14">
+        <v>2.3769999999999998</v>
+      </c>
+      <c r="G190" s="15">
+        <v>0.80249300000000001</v>
+      </c>
+      <c r="H190" s="15">
+        <v>2.0474999999999999</v>
+      </c>
+      <c r="I190" s="15">
+        <v>0.296184</v>
+      </c>
+      <c r="J190" s="15">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="K190" s="219">
+        <v>4.3986000000000001</v>
+      </c>
+      <c r="L190" s="221">
+        <v>0.501</v>
+      </c>
+      <c r="M190" s="14">
+        <v>0.98639999999999906</v>
+      </c>
+      <c r="N190" s="15">
+        <v>1.0894999999999999</v>
+      </c>
+      <c r="O190" s="15">
+        <v>6.8700000000000205E-2</v>
+      </c>
+      <c r="P190" s="219">
+        <v>3.835</v>
+      </c>
+      <c r="Q190" s="219"/>
+      <c r="R190" s="219">
+        <v>0.105</v>
+      </c>
+      <c r="S190" s="221"/>
+    </row>
+    <row r="191" spans="5:19">
+      <c r="E191" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="223"/>
+      <c r="G191" s="18">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="H191" s="18">
+        <v>0.7036</v>
+      </c>
+      <c r="I191" s="18">
+        <v>0.223</v>
+      </c>
+      <c r="J191" s="18">
+        <v>2.7959999999999999E-3</v>
+      </c>
+      <c r="K191" s="220">
+        <v>1E-3</v>
+      </c>
+      <c r="L191" s="222"/>
+      <c r="M191" s="17">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="N191" s="18">
+        <v>0.247</v>
+      </c>
+      <c r="O191" s="18">
+        <v>0.22289999999999999</v>
+      </c>
+      <c r="P191" s="220">
+        <v>2.8E-3</v>
+      </c>
+      <c r="Q191" s="220"/>
+      <c r="R191" s="220"/>
+      <c r="S191" s="222"/>
+    </row>
+    <row r="193" spans="5:19">
+      <c r="E193" s="227" t="s">
+        <v>38</v>
+      </c>
+      <c r="F193" s="228"/>
+      <c r="G193" s="228"/>
+      <c r="H193" s="228"/>
+      <c r="I193" s="228"/>
+      <c r="J193" s="228"/>
+      <c r="K193" s="228"/>
+      <c r="L193" s="228"/>
+      <c r="M193" s="228"/>
+      <c r="N193" s="228"/>
+      <c r="O193" s="228"/>
+      <c r="P193" s="228"/>
+      <c r="Q193" s="228"/>
+      <c r="R193" s="228"/>
+      <c r="S193" s="229"/>
+    </row>
+    <row r="195" spans="5:19">
+      <c r="E195" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F195" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="G195" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H195" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="I195" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="J195" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="K195" s="42" t="s">
+        <v>5</v>
+      </c>
+      <c r="L195" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="M195" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="N195" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="O195" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="P195" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q195" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="R195" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="S195" s="43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="5:19">
+      <c r="E196" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="F196" s="206">
+        <v>9.9905462085300697E-2</v>
+      </c>
+      <c r="G196" s="207">
+        <v>-7.2601803864568104E-2</v>
+      </c>
+      <c r="H196" s="207">
+        <v>3.3104325729460801E-2</v>
+      </c>
+      <c r="I196" s="207">
+        <v>-0.384545089398381</v>
+      </c>
+      <c r="J196" s="207">
+        <v>-0.32985234713682898</v>
+      </c>
+      <c r="K196" s="207">
+        <v>-0.15127604366056699</v>
+      </c>
+      <c r="L196" s="208">
+        <v>-0.168260848967065</v>
+      </c>
+      <c r="M196" s="206">
+        <v>-6.80338487428752E-2</v>
+      </c>
+      <c r="N196" s="207">
+        <v>6.1727562713571403E-2</v>
+      </c>
+      <c r="O196" s="207">
+        <v>-0.184205855358412</v>
+      </c>
+      <c r="P196" s="207">
+        <v>0.36603130909763198</v>
+      </c>
+      <c r="Q196" s="207">
+        <v>0.298722828774653</v>
+      </c>
+      <c r="R196" s="207">
+        <v>-0.109675134137715</v>
+      </c>
+      <c r="S196" s="208">
+        <v>8.4202653872626598E-2</v>
+      </c>
+    </row>
+    <row r="197" spans="5:19">
+      <c r="E197" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="F197" s="209">
+        <v>-8.1173198711979894E-2</v>
+      </c>
+      <c r="G197" s="210">
+        <v>-0.176773261280325</v>
+      </c>
+      <c r="H197" s="210">
+        <v>-5.1934771054012504E-3</v>
+      </c>
+      <c r="I197" s="210">
+        <v>-0.40068279512885502</v>
+      </c>
+      <c r="J197" s="210">
+        <v>-0.25984604752915602</v>
+      </c>
+      <c r="K197" s="210">
+        <v>-0.120545263866407</v>
+      </c>
+      <c r="L197" s="211">
+        <v>-0.18571041586088999</v>
+      </c>
+      <c r="M197" s="209">
+        <v>-0.132620596724013</v>
+      </c>
+      <c r="N197" s="210">
+        <v>-4.4729627382706902E-2</v>
+      </c>
+      <c r="O197" s="210">
+        <v>-0.205072645035279</v>
+      </c>
+      <c r="P197" s="210"/>
+      <c r="Q197" s="210"/>
+      <c r="R197" s="210">
+        <v>-5.5175502387183703E-2</v>
+      </c>
+      <c r="S197" s="211">
+        <v>2.6651717174692498E-2</v>
+      </c>
+    </row>
+    <row r="198" spans="5:19">
+      <c r="E198" s="45" t="s">
+        <v>2</v>
+      </c>
+      <c r="F198" s="209">
+        <v>3.3159195074470599E-2</v>
+      </c>
+      <c r="G198" s="210">
+        <v>-7.7078482383726304E-2</v>
+      </c>
+      <c r="H198" s="210">
+        <v>0.10829855369722401</v>
+      </c>
+      <c r="I198" s="210">
+        <v>-0.390948541971536</v>
+      </c>
+      <c r="J198" s="210">
+        <v>-0.19486807230709599</v>
+      </c>
+      <c r="K198" s="210">
+        <v>-0.14538102977964101</v>
+      </c>
+      <c r="L198" s="211">
+        <v>-0.21446674640934801</v>
+      </c>
+      <c r="M198" s="209">
+        <v>1.23261300307289E-2</v>
+      </c>
+      <c r="N198" s="210">
+        <v>8.1821481175145996E-2</v>
+      </c>
+      <c r="O198" s="210">
+        <v>-8.0032070231368893E-2</v>
+      </c>
+      <c r="P198" s="210">
+        <v>0.34496642484183798</v>
+      </c>
+      <c r="Q198" s="210">
+        <v>0.24975132998221899</v>
+      </c>
+      <c r="R198" s="210">
+        <v>-1.2894031578603299E-2</v>
+      </c>
+      <c r="S198" s="211">
+        <v>9.3962488834249305E-2</v>
+      </c>
+    </row>
+    <row r="199" spans="5:19">
+      <c r="E199" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="F199" s="209">
+        <v>3.1985990939469501E-2</v>
+      </c>
+      <c r="G199" s="210">
+        <v>2.28579145681252E-2</v>
+      </c>
+      <c r="H199" s="210">
+        <v>3.8789976135843299E-2</v>
+      </c>
+      <c r="I199" s="210">
+        <v>0</v>
+      </c>
+      <c r="J199" s="210"/>
+      <c r="K199" s="210">
+        <v>-2.49383769471671E-3</v>
+      </c>
+      <c r="L199" s="211">
+        <v>-5.7678642737837897E-2</v>
+      </c>
+      <c r="M199" s="209">
+        <v>7.4148555518791598E-2</v>
+      </c>
+      <c r="N199" s="210">
+        <v>0.106569445993788</v>
+      </c>
+      <c r="O199" s="210">
+        <v>1.2328042328042301E-2</v>
+      </c>
+      <c r="P199" s="210">
+        <v>0.36558225170138697</v>
+      </c>
+      <c r="Q199" s="210"/>
+      <c r="R199" s="210">
+        <v>0.134094410099142</v>
+      </c>
+      <c r="S199" s="211">
+        <v>0.145409445815848</v>
+      </c>
+    </row>
+    <row r="200" spans="5:19">
+      <c r="E200" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F200" s="209">
+        <v>0.19694921070167601</v>
+      </c>
+      <c r="G200" s="210">
+        <v>0.120979461180703</v>
+      </c>
+      <c r="H200" s="210">
+        <v>0.28487052413991099</v>
+      </c>
+      <c r="I200" s="210">
+        <v>-0.36103413494717801</v>
+      </c>
+      <c r="J200" s="210"/>
+      <c r="K200" s="210"/>
+      <c r="L200" s="211"/>
+      <c r="M200" s="209">
+        <v>0.115933945367974</v>
+      </c>
+      <c r="N200" s="210">
+        <v>0.20617675130274299</v>
+      </c>
+      <c r="O200" s="210">
+        <v>2.69405539993775E-2</v>
+      </c>
+      <c r="P200" s="210">
+        <v>0.39425803969509099</v>
+      </c>
+      <c r="Q200" s="210">
+        <v>0.41304347826086901</v>
+      </c>
+      <c r="R200" s="210">
+        <v>-3.8461538461538401E-2</v>
+      </c>
+      <c r="S200" s="211"/>
+    </row>
+    <row r="201" spans="5:19">
+      <c r="E201" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="F201" s="209">
+        <v>0.33908320674796699</v>
+      </c>
+      <c r="G201" s="210">
+        <v>0.23677356768543401</v>
+      </c>
+      <c r="H201" s="210">
+        <v>0.32954592453568798</v>
+      </c>
+      <c r="I201" s="210">
+        <v>-0.279464285714285</v>
+      </c>
+      <c r="J201" s="210"/>
+      <c r="K201" s="210">
+        <v>0.35714285714285698</v>
+      </c>
+      <c r="L201" s="211"/>
+      <c r="M201" s="209">
+        <v>0.13035594497073599</v>
+      </c>
+      <c r="N201" s="210">
+        <v>0.34376156091940602</v>
+      </c>
+      <c r="O201" s="210">
+        <v>0.19541489470282</v>
+      </c>
+      <c r="P201" s="210">
+        <v>0.40244432902765298</v>
+      </c>
+      <c r="Q201" s="210">
+        <v>0.41224468679849002</v>
+      </c>
+      <c r="R201" s="210"/>
+      <c r="S201" s="211"/>
+    </row>
+    <row r="202" spans="5:19">
+      <c r="E202" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="F202" s="212">
+        <v>0.38992800887755702</v>
+      </c>
+      <c r="G202" s="213">
+        <v>0.357343879573842</v>
+      </c>
+      <c r="H202" s="213">
+        <v>0.35695961707289903</v>
+      </c>
+      <c r="I202" s="213"/>
+      <c r="J202" s="213">
+        <v>0</v>
+      </c>
+      <c r="K202" s="213"/>
+      <c r="L202" s="214">
+        <v>0.3</v>
+      </c>
+      <c r="M202" s="212"/>
+      <c r="N202" s="213">
+        <v>0.38542534102252002</v>
+      </c>
+      <c r="O202" s="213">
+        <v>0.248404681738015</v>
+      </c>
+      <c r="P202" s="213">
+        <v>0.39877648109313402</v>
+      </c>
+      <c r="Q202" s="213">
+        <v>0.39245611541791697</v>
+      </c>
+      <c r="R202" s="213">
+        <v>0.28125</v>
+      </c>
+      <c r="S202" s="214">
+        <v>0.44999999999999901</v>
+      </c>
+    </row>
+    <row r="203" spans="5:19">
+      <c r="E203" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F203" s="80">
+        <v>4.1586665171067003E-2</v>
+      </c>
+      <c r="G203" s="81">
+        <v>-8.4605593533508897E-2</v>
+      </c>
+      <c r="H203" s="81">
+        <v>0.12356175481079799</v>
+      </c>
+      <c r="I203" s="81">
+        <v>-0.36471606551218499</v>
+      </c>
+      <c r="J203" s="81">
+        <v>-0.33753575166835897</v>
+      </c>
+      <c r="K203" s="81">
+        <v>7.2770796237683996E-2</v>
+      </c>
+      <c r="L203" s="82">
+        <v>-0.13257378720835999</v>
+      </c>
+      <c r="M203" s="80">
+        <v>-0.117936186435812</v>
+      </c>
+      <c r="N203" s="81">
+        <v>4.2214444254743397E-2</v>
+      </c>
+      <c r="O203" s="81">
+        <v>-5.5619169979571802E-2</v>
+      </c>
+      <c r="P203" s="81">
+        <v>0.36719089112522002</v>
+      </c>
+      <c r="Q203" s="81">
+        <v>0.308848626330535</v>
+      </c>
+      <c r="R203" s="81">
+        <v>0.11748042164024999</v>
+      </c>
+      <c r="S203" s="82">
+        <v>0.14822179182482301</v>
+      </c>
+    </row>
+    <row r="204" spans="5:19">
+      <c r="E204" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F204" s="83">
+        <v>0.105993129702547</v>
+      </c>
+      <c r="G204" s="84">
+        <v>3.23762273213794E-3</v>
+      </c>
+      <c r="H204" s="84">
+        <v>0.19352969658929201</v>
+      </c>
+      <c r="I204" s="84"/>
+      <c r="J204" s="84"/>
+      <c r="K204" s="84">
+        <v>5.6159035224220402E-2</v>
+      </c>
+      <c r="L204" s="85">
+        <v>-4.8860835479998102E-2</v>
+      </c>
+      <c r="M204" s="83">
+        <v>5.3262323374033103E-2</v>
+      </c>
+      <c r="N204" s="84">
+        <v>0.15463285289956599</v>
+      </c>
+      <c r="O204" s="84">
+        <v>-3.08709378471714E-2</v>
+      </c>
+      <c r="P204" s="84">
+        <v>0.39061055793615201</v>
+      </c>
+      <c r="Q204" s="84">
+        <v>0.25572286157304402</v>
+      </c>
+      <c r="R204" s="84">
+        <v>8.3214842135471201E-2</v>
+      </c>
+      <c r="S204" s="85">
+        <v>0.143943452105049</v>
+      </c>
+    </row>
+    <row r="205" spans="5:19">
+      <c r="E205" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F205" s="83">
+        <v>-4.8967910079383802E-2</v>
+      </c>
+      <c r="G205" s="84">
+        <v>-9.5762791038125697E-2</v>
+      </c>
+      <c r="H205" s="84">
+        <v>5.8688261932670099E-2</v>
+      </c>
+      <c r="I205" s="84">
+        <v>-0.34296259052245398</v>
+      </c>
+      <c r="J205" s="84">
+        <v>-0.30051994156900402</v>
+      </c>
+      <c r="K205" s="84">
+        <v>-5.2145470276465801E-2</v>
+      </c>
+      <c r="L205" s="85">
+        <v>-1.47383467266508E-2</v>
+      </c>
+      <c r="M205" s="83">
+        <v>-4.4926539793208098E-2</v>
+      </c>
+      <c r="N205" s="84">
+        <v>3.55764793665388E-2</v>
+      </c>
+      <c r="O205" s="84">
+        <v>-8.0686439156473194E-2</v>
+      </c>
+      <c r="P205" s="84">
+        <v>0.38756219702384898</v>
+      </c>
+      <c r="Q205" s="84">
+        <v>0.16215221256593201</v>
+      </c>
+      <c r="R205" s="84">
+        <v>0.20848208718219999</v>
+      </c>
+      <c r="S205" s="85">
+        <v>2.2248427672955901E-2</v>
+      </c>
+    </row>
+    <row r="206" spans="5:19">
+      <c r="E206" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F206" s="83">
         <v>-0.10869923311280399</v>
       </c>
-      <c r="G126" s="84">
+      <c r="G206" s="84">
         <v>-0.13534476720791999</v>
       </c>
-      <c r="H126" s="84">
+      <c r="H206" s="84">
         <v>-0.257411216234745</v>
       </c>
-      <c r="I126" s="84">
+      <c r="I206" s="84">
         <v>-0.38767214143483603</v>
       </c>
-      <c r="J126" s="84"/>
-      <c r="K126" s="84">
+      <c r="J206" s="84"/>
+      <c r="K206" s="84">
         <v>-0.15346453607190999</v>
       </c>
-      <c r="L126" s="85">
+      <c r="L206" s="85">
         <v>-0.18553675565639899</v>
       </c>
-      <c r="M126" s="83">
+      <c r="M206" s="83">
         <v>-9.1375411825098202E-2</v>
       </c>
-      <c r="N126" s="84">
+      <c r="N206" s="84">
         <v>-5.4961778811326002E-2</v>
       </c>
-      <c r="O126" s="84">
+      <c r="O206" s="84">
         <v>-9.9168283870669199E-2</v>
       </c>
-      <c r="P126" s="84"/>
-      <c r="Q126" s="84"/>
-      <c r="R126" s="84">
+      <c r="P206" s="84"/>
+      <c r="Q206" s="84"/>
+      <c r="R206" s="84">
         <v>-4.3052807037969501E-2</v>
       </c>
-      <c r="S126" s="85">
+      <c r="S206" s="85">
         <v>5.4063911344650897E-2</v>
       </c>
     </row>
-    <row r="127" spans="5:19">
-      <c r="E127" s="45" t="s">
+    <row r="207" spans="5:19">
+      <c r="E207" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="F127" s="83">
+      <c r="F207" s="83">
         <v>-0.125795291419843</v>
       </c>
-      <c r="G127" s="84">
+      <c r="G207" s="84">
         <v>-0.20079693324960901</v>
       </c>
-      <c r="H127" s="84">
+      <c r="H207" s="84">
         <v>-6.0068926014448402E-2</v>
       </c>
-      <c r="I127" s="84">
+      <c r="I207" s="84">
         <v>-0.39131950347877797</v>
       </c>
-      <c r="J127" s="84"/>
-      <c r="K127" s="84">
+      <c r="J207" s="84"/>
+      <c r="K207" s="84">
         <v>-0.233333333333333</v>
       </c>
-      <c r="L127" s="85"/>
-      <c r="M127" s="83">
+      <c r="L207" s="85"/>
+      <c r="M207" s="83">
         <v>-0.17313153661668901</v>
       </c>
-      <c r="N127" s="84">
+      <c r="N207" s="84">
         <v>-0.107232021944899</v>
       </c>
-      <c r="O127" s="84">
+      <c r="O207" s="84">
         <v>-0.29422186747325002</v>
       </c>
-      <c r="P127" s="84">
+      <c r="P207" s="84">
         <v>0.34502801120448101</v>
       </c>
-      <c r="Q127" s="84"/>
-      <c r="R127" s="84">
+      <c r="Q207" s="84"/>
+      <c r="R207" s="84">
         <v>7.5367647058823498E-2</v>
       </c>
-      <c r="S127" s="85">
+      <c r="S207" s="85">
         <v>0.23076923076923</v>
       </c>
     </row>
-    <row r="128" spans="5:19">
-      <c r="E128" s="45" t="s">
+    <row r="208" spans="5:19">
+      <c r="E208" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="F128" s="83">
+      <c r="F208" s="83">
         <v>-0.14225900486405399</v>
       </c>
-      <c r="G128" s="84">
+      <c r="G208" s="84">
         <v>-0.35256604791558899</v>
       </c>
-      <c r="H128" s="84">
+      <c r="H208" s="84">
         <v>-0.20990667874799099</v>
       </c>
-      <c r="I128" s="84">
+      <c r="I208" s="84">
         <v>-0.42418563288634198</v>
       </c>
-      <c r="J128" s="84">
+      <c r="J208" s="84">
         <v>-0.42031681118236802</v>
       </c>
-      <c r="K128" s="84">
+      <c r="K208" s="84">
         <v>-8.8888888888888795E-2</v>
       </c>
-      <c r="L128" s="85">
+      <c r="L208" s="85">
         <v>-0.25</v>
       </c>
-      <c r="M128" s="83">
+      <c r="M208" s="83">
         <v>-0.32327700001642401</v>
       </c>
-      <c r="N128" s="84">
+      <c r="N208" s="84">
         <v>-0.280052382866877</v>
       </c>
-      <c r="O128" s="84">
+      <c r="O208" s="84">
         <v>-0.36169361958481</v>
       </c>
-      <c r="P128" s="84">
+      <c r="P208" s="84">
         <v>0.30720899470899399</v>
       </c>
-      <c r="Q128" s="84"/>
-      <c r="R128" s="84">
+      <c r="Q208" s="84"/>
+      <c r="R208" s="84">
         <v>-0.11128346961680199</v>
       </c>
-      <c r="S128" s="85"/>
-    </row>
-    <row r="129" spans="5:19">
-      <c r="E129" s="46" t="s">
+      <c r="S208" s="85"/>
+    </row>
+    <row r="209" spans="5:19">
+      <c r="E209" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F129" s="86"/>
-      <c r="G129" s="87">
+      <c r="F209" s="86"/>
+      <c r="G209" s="87">
         <v>-0.38830092303146502</v>
       </c>
-      <c r="H129" s="87">
+      <c r="H209" s="87">
         <v>-0.396267621267621</v>
       </c>
-      <c r="I129" s="87">
+      <c r="I209" s="87">
         <v>-0.41676199191725499</v>
       </c>
-      <c r="J129" s="87">
+      <c r="J209" s="87">
         <v>-0.31212121212121202</v>
       </c>
-      <c r="K129" s="87">
+      <c r="K209" s="87">
         <v>-0.40909090909090901</v>
       </c>
-      <c r="L129" s="88"/>
-      <c r="M129" s="86">
+      <c r="L209" s="88"/>
+      <c r="M209" s="86">
         <v>-0.40103340769038598</v>
       </c>
-      <c r="N129" s="87">
+      <c r="N209" s="87">
         <v>-0.36948693633829899</v>
       </c>
-      <c r="O129" s="87">
+      <c r="O209" s="87">
         <v>-0.35589011335486098</v>
       </c>
-      <c r="P129" s="87">
+      <c r="P209" s="87">
         <v>-0.15</v>
       </c>
-      <c r="Q129" s="87"/>
-      <c r="R129" s="87"/>
-      <c r="S129" s="88"/>
+      <c r="Q209" s="87"/>
+      <c r="R209" s="87"/>
+      <c r="S209" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="E113:S113"/>
+    <mergeCell ref="E193:S193"/>
     <mergeCell ref="E22:S22"/>
     <mergeCell ref="E41:S41"/>
     <mergeCell ref="E59:S59"/>
@@ -14882,6 +18532,114 @@
     <mergeCell ref="E95:S95"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C20">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:S20">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:S3">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V7:V20">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y7:Y20">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F98:S111">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F44:S57">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F80:S93">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F196:S209">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF0000"/>
+        <color theme="0"/>
+        <color rgb="FF00B0F0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:S38">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -14893,7 +18651,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:S20">
+  <conditionalFormatting sqref="C25:C38">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -14905,7 +18663,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:S3">
+  <conditionalFormatting sqref="V62:V75">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -14917,116 +18675,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V7:V20">
+  <conditionalFormatting sqref="Y62:Y75">
     <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y7:Y20">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F98:S111">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F44:S57">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F80:S93">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F116:S129">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:S38">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C25:C38">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V62:V75">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFF0000"/>
-        <color theme="0"/>
-        <color rgb="FF00B0F0"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y62:Y75">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -15040,6 +18690,107 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="9" id="{6CE73B24-354B-0C40-AEF6-BF62018A9BF6}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>1E-3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0.01</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3ArrowsGray" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F114:S127</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="4" id="{2B0176FE-5006-D04D-8084-E6B9B28E4BB6}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>1E-3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0.01</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3ArrowsGray" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F130:S143</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="3" id="{1133DF39-9436-0F4B-B3F7-4B512642759A}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>1E-3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0.01</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3ArrowsGray" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F146:S159</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{B48C4910-B75C-D04D-85E5-290A9EF68CE0}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>1E-3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0.01</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3ArrowsGray" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F162:S175</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{4326E029-2AEC-C341-BDC9-85A8F8B7F568}">
+            <x14:iconSet custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>1E-3</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0.01</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Arrows" iconId="0"/>
+              <x14:cfIcon iconSet="3ArrowsGray" iconId="1"/>
+              <x14:cfIcon iconSet="3Arrows" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>F178:S191</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -16172,29 +19923,23 @@
       </c>
     </row>
     <row r="22" spans="2:25">
-      <c r="B22" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="25">
-        <v>38500</v>
-      </c>
-      <c r="E22" s="215" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="216"/>
-      <c r="G22" s="216"/>
-      <c r="H22" s="216"/>
-      <c r="I22" s="216"/>
-      <c r="J22" s="216"/>
-      <c r="K22" s="216"/>
-      <c r="L22" s="216"/>
-      <c r="M22" s="216"/>
-      <c r="N22" s="216"/>
-      <c r="O22" s="216"/>
-      <c r="P22" s="216"/>
-      <c r="Q22" s="216"/>
-      <c r="R22" s="216"/>
-      <c r="S22" s="217"/>
+      <c r="E22" s="227" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="228"/>
+      <c r="G22" s="228"/>
+      <c r="H22" s="228"/>
+      <c r="I22" s="228"/>
+      <c r="J22" s="228"/>
+      <c r="K22" s="228"/>
+      <c r="L22" s="228"/>
+      <c r="M22" s="228"/>
+      <c r="N22" s="228"/>
+      <c r="O22" s="228"/>
+      <c r="P22" s="228"/>
+      <c r="Q22" s="228"/>
+      <c r="R22" s="228"/>
+      <c r="S22" s="229"/>
       <c r="V22" s="54">
         <f>Y22/V3</f>
         <v>14.847627627627627</v>
@@ -16259,52 +20004,52 @@
         <v>0</v>
       </c>
       <c r="C25" s="8">
-        <v>1.51878045467599</v>
+        <v>0.32656508639475701</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F25" s="11">
-        <v>0.34290918891870298</v>
+        <v>0.53439679153989506</v>
       </c>
       <c r="G25" s="12">
-        <v>0.16423602524624401</v>
+        <v>0.208918128436096</v>
       </c>
       <c r="H25" s="12">
-        <v>6.2712640609646E-2</v>
+        <v>0.15364365669777699</v>
       </c>
       <c r="I25" s="12">
-        <v>0.36572264970714102</v>
+        <v>1.01060412213221</v>
       </c>
       <c r="J25" s="12">
-        <v>0.36535014982306602</v>
+        <v>1.0076350255948301</v>
       </c>
       <c r="K25" s="12">
-        <v>0.16338882025226001</v>
+        <v>0.26193699358884698</v>
       </c>
       <c r="L25" s="13">
-        <v>4.7904302167658397E-2</v>
+        <v>7.6813970104440896E-2</v>
       </c>
       <c r="M25" s="11">
-        <v>1.60094230504375E-2</v>
+        <v>9.8647251409155392E-3</v>
       </c>
       <c r="N25" s="12">
-        <v>1.12830138940898E-2</v>
+        <v>4.0502510756987103E-2</v>
       </c>
       <c r="O25" s="12">
-        <v>1.68229278805666E-2</v>
+        <v>0.20032565388161999</v>
       </c>
       <c r="P25" s="12">
-        <v>3.21399249714295E-2</v>
+        <v>2.0225567919987E-2</v>
       </c>
       <c r="Q25" s="12">
-        <v>8.3855704990413296E-2</v>
+        <v>1.0501007796077599E-2</v>
       </c>
       <c r="R25" s="12">
-        <v>7.6871845331219005E-2</v>
+        <v>2.0267629703473799E-2</v>
       </c>
       <c r="S25" s="13">
-        <v>7.2209697514414195E-2</v>
+        <v>2.1897310357370799E-2</v>
       </c>
     </row>
     <row r="26" spans="2:25">
@@ -16312,52 +20057,52 @@
         <v>1</v>
       </c>
       <c r="C26" s="9">
-        <v>1.0609337161347201</v>
+        <v>0.15881169619809099</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F26" s="14">
-        <v>9.19475032400391E-2</v>
+        <v>0.111592522534326</v>
       </c>
       <c r="G26" s="15">
-        <v>0.327374230271535</v>
+        <v>0.58230812865316195</v>
       </c>
       <c r="H26" s="15">
-        <v>4.15683675079149E-2</v>
+        <v>8.1213275582894595E-2</v>
       </c>
       <c r="I26" s="15">
-        <v>7.6154028047043396E-2</v>
+        <v>0.18889120097992701</v>
       </c>
       <c r="J26" s="15">
-        <v>1.9634368755259E-2</v>
+        <v>0.61045002356577804</v>
       </c>
       <c r="K26" s="15">
-        <v>2.41526805660577E-2</v>
+        <v>0.41124849023777899</v>
       </c>
       <c r="L26" s="16">
-        <v>5.8171359160926403E-2</v>
+        <v>0.39304555455103901</v>
       </c>
       <c r="M26" s="14">
-        <v>3.1708912530308601E-2</v>
+        <v>5.1477376326977999E-2</v>
       </c>
       <c r="N26" s="15">
-        <v>2.5552260374807199E-2</v>
+        <v>9.8972261903816604E-3</v>
       </c>
       <c r="O26" s="15">
-        <v>1.89301622362744E-2</v>
+        <v>7.7582368000989497E-3</v>
       </c>
       <c r="P26" s="15">
-        <v>-4.5989399694985403E-2</v>
+        <v>0.159368834651548</v>
       </c>
       <c r="Q26" s="15">
-        <v>-4.31746921803252E-2</v>
+        <v>0.30445201740358102</v>
       </c>
       <c r="R26" s="15">
-        <v>4.6158074499946598E-2</v>
+        <v>7.5686855708632199E-3</v>
       </c>
       <c r="S26" s="16">
-        <v>5.6753234879983003E-2</v>
+        <v>9.5587182686938197E-3</v>
       </c>
     </row>
     <row r="27" spans="2:25">
@@ -16365,52 +20110,52 @@
         <v>2</v>
       </c>
       <c r="C27" s="9">
-        <v>0.51150771852670396</v>
+        <v>8.7142337447612697E-2</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F27" s="14">
-        <v>6.5067782908926498E-3</v>
+        <v>3.8238306042914401E-3</v>
       </c>
       <c r="G27" s="15">
-        <v>2.01343346202001E-2</v>
+        <v>1.8884082714394498E-2</v>
       </c>
       <c r="H27" s="15">
-        <v>0.201700056144517</v>
+        <v>0.62446299502240599</v>
       </c>
       <c r="I27" s="15">
-        <v>-3.8318697444796302E-3</v>
+        <v>1.8704434440970699E-3</v>
       </c>
       <c r="J27" s="15">
-        <v>-2.35319917380142E-2</v>
+        <v>9.9573935229384097E-2</v>
       </c>
       <c r="K27" s="15">
-        <v>-4.9210180220441999E-3</v>
+        <v>9.0530593873892604E-2</v>
       </c>
       <c r="L27" s="16">
-        <v>-1.5982733683854399E-2</v>
+        <v>2.9191684597380699E-2</v>
       </c>
       <c r="M27" s="14">
-        <v>2.9324698691545899E-3</v>
+        <v>8.2629180355789297E-3</v>
       </c>
       <c r="N27" s="15">
-        <v>3.6562217758992202E-3</v>
+        <v>1.9019985600615501E-4</v>
       </c>
       <c r="O27" s="15">
-        <v>-1.8903609568762299E-3</v>
+        <v>3.0886152018500299E-2</v>
       </c>
       <c r="P27" s="15">
-        <v>3.0005585868270599E-2</v>
+        <v>0.110993848971989</v>
       </c>
       <c r="Q27" s="15">
-        <v>9.9526994719980805E-2</v>
+        <v>0.312605741188067</v>
       </c>
       <c r="R27" s="15">
-        <v>1.91760887137298E-3</v>
+        <v>3.50024459481679E-3</v>
       </c>
       <c r="S27" s="16">
-        <v>-3.6364808625553502E-3</v>
+        <v>8.3639751334957794E-5</v>
       </c>
     </row>
     <row r="28" spans="2:25">
@@ -16418,52 +20163,52 @@
         <v>3</v>
       </c>
       <c r="C28" s="9">
-        <v>0.13294626140538701</v>
+        <v>0</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F28" s="14">
-        <v>6.6583095926289297E-3</v>
+        <v>2.1048086623369901E-3</v>
       </c>
       <c r="G28" s="15">
-        <v>5.9456003485464804E-3</v>
+        <v>1.20224333220519E-3</v>
       </c>
       <c r="H28" s="15">
-        <v>5.4136263962473001E-3</v>
+        <v>5.3818686443046502E-3</v>
       </c>
       <c r="I28" s="15">
-        <v>-4.5749812573497403E-2</v>
+        <v>8.0622820918403596E-5</v>
       </c>
       <c r="J28" s="15">
-        <v>9.2771056865262498E-4</v>
+        <v>1.7428908025779601E-16</v>
       </c>
       <c r="K28" s="15">
-        <v>0.293532844545701</v>
+        <v>0.57390508830068099</v>
       </c>
       <c r="L28" s="16">
-        <v>0.21227460063978301</v>
+        <v>0.37004578472524202</v>
       </c>
       <c r="M28" s="14">
-        <v>1.852603113978E-3</v>
+        <v>3.3507621468014402E-5</v>
       </c>
       <c r="N28" s="15">
-        <v>3.8995790992995098E-3</v>
+        <v>9.5803227538680498E-6</v>
       </c>
       <c r="O28" s="15">
-        <v>-2.0026374279151901E-3</v>
+        <v>3.3895475825775903E-5</v>
       </c>
       <c r="P28" s="15">
-        <v>-2.5623802121329E-2</v>
+        <v>1.37338740807882E-4</v>
       </c>
       <c r="Q28" s="15">
-        <v>5.3316678159957697E-5</v>
+        <v>1.2483379758115201E-3</v>
       </c>
       <c r="R28" s="15">
-        <v>8.7873805544218003E-2</v>
+        <v>0.36247232041524802</v>
       </c>
       <c r="S28" s="16">
-        <v>0.12544486596770599</v>
+        <v>0.54215245470557305</v>
       </c>
     </row>
     <row r="29" spans="2:25">
@@ -16471,52 +20216,52 @@
         <v>4</v>
       </c>
       <c r="C29" s="9">
-        <v>8.5249938709489201E-2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F29" s="14">
-        <v>7.3428168762472196E-4</v>
+        <v>6.4735619007183303E-4</v>
       </c>
       <c r="G29" s="15">
-        <v>2.68145138660133E-3</v>
+        <v>2.0944132207466101E-3</v>
       </c>
       <c r="H29" s="15">
-        <v>1.1696661238548499E-2</v>
+        <v>2.03235321056707E-2</v>
       </c>
       <c r="I29" s="15">
-        <v>-1.1890443654909301E-3</v>
+        <v>1.82508855883644E-5</v>
       </c>
       <c r="J29" s="15">
-        <v>-6.9168551419427201E-3</v>
+        <v>1.31506554803287E-3</v>
       </c>
       <c r="K29" s="15">
-        <v>-2.8292145454133599E-4</v>
+        <v>7.8886779701397295E-5</v>
       </c>
       <c r="L29" s="16">
-        <v>-2.4190675601199899E-3</v>
+        <v>1.51600853062668E-4</v>
       </c>
       <c r="M29" s="14">
-        <v>4.3541973799632598E-4</v>
+        <v>3.1558224771092302E-4</v>
       </c>
       <c r="N29" s="15">
-        <v>1.04071376466153E-3</v>
+        <v>1.4104781427763801E-5</v>
       </c>
       <c r="O29" s="15">
-        <v>1.8776987287010599E-3</v>
+        <v>2.93634009757138E-4</v>
       </c>
       <c r="P29" s="15">
-        <v>1.6652889393492101E-2</v>
+        <v>5.7259188017270403E-2</v>
       </c>
       <c r="Q29" s="15">
-        <v>1.5887867271555299E-2</v>
+        <v>0.121430702124983</v>
       </c>
       <c r="R29" s="15">
-        <v>-7.4132993144363304E-4</v>
+        <v>4.8255277507531E-4</v>
       </c>
       <c r="S29" s="16">
-        <v>-2.2129469415506698E-3</v>
+        <v>6.1038922117493503E-3</v>
       </c>
     </row>
     <row r="30" spans="2:25">
@@ -16524,52 +20269,52 @@
         <v>5</v>
       </c>
       <c r="C30" s="9">
-        <v>0.13421815606965401</v>
+        <v>0</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F30" s="14">
-        <v>1.83208303264696E-3</v>
+        <v>1.7305069988485999E-3</v>
       </c>
       <c r="G30" s="15">
-        <v>3.9578120638380397E-3</v>
+        <v>8.4330329036488901E-3</v>
       </c>
       <c r="H30" s="15">
-        <v>3.5579166521506202E-2</v>
+        <v>3.7294870931991103E-2</v>
       </c>
       <c r="I30" s="15">
-        <v>-5.7424980006844204E-4</v>
+        <v>0.12604946492254701</v>
       </c>
       <c r="J30" s="15">
-        <v>-8.3296327018268397E-3</v>
+        <v>7.8887687827180802E-4</v>
       </c>
       <c r="K30" s="15">
-        <v>-3.4199993617240101E-3</v>
+        <v>7.2376822344599496E-4</v>
       </c>
       <c r="L30" s="16">
-        <v>-4.8346899889139304E-3</v>
+        <v>4.0682917152836798E-5</v>
       </c>
       <c r="M30" s="14">
-        <v>2.10180643715618E-4</v>
+        <v>4.7604465200490998E-4</v>
       </c>
       <c r="N30" s="15">
-        <v>2.1845906385754899E-3</v>
+        <v>3.4153375194627899E-5</v>
       </c>
       <c r="O30" s="15">
-        <v>-1.2105996960914201E-3</v>
+        <v>2.47413458411448E-4</v>
       </c>
       <c r="P30" s="15">
-        <v>2.14787498183973E-2</v>
+        <v>0.242473847419309</v>
       </c>
       <c r="Q30" s="15">
-        <v>2.7682651146701501E-2</v>
+        <v>0.214922166447926</v>
       </c>
       <c r="R30" s="15">
-        <v>-4.2001976817851498E-4</v>
+        <v>5.2641848190817196E-4</v>
       </c>
       <c r="S30" s="16">
-        <v>-1.8869013839578599E-3</v>
+        <v>7.1385009658932403E-4</v>
       </c>
     </row>
     <row r="31" spans="2:25">
@@ -16577,52 +20322,52 @@
         <v>6</v>
       </c>
       <c r="C31" s="10">
-        <v>9.6449970484074193E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>6</v>
       </c>
       <c r="F31" s="17">
-        <v>1.23030981709017E-3</v>
+        <v>2.5123739319249199E-4</v>
       </c>
       <c r="G31" s="18">
-        <v>5.6400570088690899E-3</v>
+        <v>2.8122196199893402E-3</v>
       </c>
       <c r="H31" s="18">
-        <v>7.3297327873314104E-3</v>
+        <v>5.7275299947236501E-3</v>
       </c>
       <c r="I31" s="18">
-        <v>-3.94311492713379E-3</v>
+        <v>2.8618013799659101E-2</v>
       </c>
       <c r="J31" s="18">
-        <v>-8.5899107052974395E-3</v>
+        <v>5.7528192197638095E-4</v>
       </c>
       <c r="K31" s="18">
-        <v>-2.0471567832920099E-3</v>
+        <v>3.2560989458688502E-4</v>
       </c>
       <c r="L31" s="19">
-        <v>-8.9884050067511501E-4</v>
+        <v>1.482483177409E-3</v>
       </c>
       <c r="M31" s="17">
-        <v>-5.6080442461608798E-4</v>
+        <v>2.4325184178124099E-33</v>
       </c>
       <c r="N31" s="18">
-        <v>2.0770921385372802E-3</v>
+        <v>1.7022094351039199E-6</v>
       </c>
       <c r="O31" s="18">
-        <v>-1.1082373319028099E-3</v>
+        <v>5.1700848642770797E-6</v>
       </c>
       <c r="P31" s="18">
-        <v>4.9233368984631397E-2</v>
+        <v>0.18665358821713901</v>
       </c>
       <c r="Q31" s="18">
-        <v>2.99657780679938E-2</v>
+        <v>0.162008381253961</v>
       </c>
       <c r="R31" s="18">
-        <v>-3.9206860755547097E-3</v>
+        <v>4.4682117970002799E-4</v>
       </c>
       <c r="S31" s="19">
-        <v>9.2188464516626802E-5</v>
+        <v>8.6249338406916402E-5</v>
       </c>
     </row>
     <row r="32" spans="2:25">
@@ -16630,52 +20375,52 @@
         <v>7</v>
       </c>
       <c r="C32" s="8">
-        <v>1.4828671095071</v>
+        <v>0.32868670138647998</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="11">
-        <v>1.5383192486147401E-2</v>
+        <v>9.5943419878085304E-3</v>
       </c>
       <c r="G32" s="12">
-        <v>1.16132993025244E-2</v>
+        <v>4.1314335673613298E-2</v>
       </c>
       <c r="H32" s="12">
-        <v>1.4300978263131901E-2</v>
+        <v>0.19686274025699299</v>
       </c>
       <c r="I32" s="12">
-        <v>2.28952673552262E-2</v>
+        <v>2.0484303152190901E-2</v>
       </c>
       <c r="J32" s="12">
-        <v>7.8130432818749304E-2</v>
+        <v>1.05767111271514E-2</v>
       </c>
       <c r="K32" s="12">
-        <v>6.9627994041383701E-2</v>
+        <v>1.75254252701477E-2</v>
       </c>
       <c r="L32" s="13">
-        <v>5.5071100481073602E-2</v>
+        <v>3.0398055431957501E-2</v>
       </c>
       <c r="M32" s="11">
-        <v>0.34049348468739599</v>
+        <v>0.53132141961165502</v>
       </c>
       <c r="N32" s="12">
-        <v>0.16339375858194899</v>
+        <v>0.20667110682019099</v>
       </c>
       <c r="O32" s="12">
-        <v>6.5933675398837793E-2</v>
+        <v>0.150491989247306</v>
       </c>
       <c r="P32" s="12">
-        <v>0.35325719458858001</v>
+        <v>1.0077160024585601</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.33388265710106302</v>
+        <v>0.99744675465120802</v>
       </c>
       <c r="R32" s="12">
-        <v>0.155435776974679</v>
+        <v>0.25977247230327299</v>
       </c>
       <c r="S32" s="13">
-        <v>6.4105953398246998E-2</v>
+        <v>8.0550946169170995E-2</v>
       </c>
     </row>
     <row r="33" spans="2:26">
@@ -16683,52 +20428,52 @@
         <v>8</v>
       </c>
       <c r="C33" s="9">
-        <v>1.09488886432123</v>
+        <v>0.16013826549298199</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F33" s="14">
-        <v>2.9380462991380699E-2</v>
+        <v>5.2068401655336299E-2</v>
       </c>
       <c r="G33" s="15">
-        <v>2.80987470351753E-2</v>
+        <v>9.7713487507640803E-3</v>
       </c>
       <c r="H33" s="15">
-        <v>2.0915047773490798E-2</v>
+        <v>7.7640184890142702E-3</v>
       </c>
       <c r="I33" s="15">
-        <v>-4.1338347684309697E-2</v>
+        <v>0.15280864184551801</v>
       </c>
       <c r="J33" s="15">
-        <v>-4.0249533350319701E-2</v>
+        <v>0.28563602348832701</v>
       </c>
       <c r="K33" s="15">
-        <v>2.9085156190909098E-2</v>
+        <v>7.8252208784440995E-3</v>
       </c>
       <c r="L33" s="16">
-        <v>6.5260339814804003E-2</v>
+        <v>1.2720747947141901E-2</v>
       </c>
       <c r="M33" s="14">
-        <v>9.0577266248633007E-2</v>
+        <v>0.112164134327725</v>
       </c>
       <c r="N33" s="15">
-        <v>0.32953092945978102</v>
+        <v>0.58436465279108796</v>
       </c>
       <c r="O33" s="15">
-        <v>4.0762039145847598E-2</v>
+        <v>8.3600813669121393E-2</v>
       </c>
       <c r="P33" s="15">
-        <v>8.1384300057729703E-2</v>
+        <v>0.183355492854963</v>
       </c>
       <c r="Q33" s="15">
-        <v>3.1344286342676601E-2</v>
+        <v>0.59071398416191701</v>
       </c>
       <c r="R33" s="15">
-        <v>3.7009666841773203E-2</v>
+        <v>0.42137575513216302</v>
       </c>
       <c r="S33" s="16">
-        <v>3.9782442538881198E-2</v>
+        <v>0.40685966021999898</v>
       </c>
     </row>
     <row r="34" spans="2:26">
@@ -16736,52 +20481,52 @@
         <v>9</v>
       </c>
       <c r="C34" s="9">
-        <v>0.499086972197469</v>
+        <v>8.4155280220345394E-2</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="14">
-        <v>3.3039268542810999E-3</v>
+        <v>7.5521531924627799E-3</v>
       </c>
       <c r="G34" s="15">
-        <v>3.9563700985586203E-3</v>
+        <v>1.9076953062495801E-4</v>
       </c>
       <c r="H34" s="15">
-        <v>-1.40582381833015E-3</v>
+        <v>2.7563254301605E-2</v>
       </c>
       <c r="I34" s="15">
-        <v>2.9204133087462E-2</v>
+        <v>0.108641744133862</v>
       </c>
       <c r="J34" s="15">
-        <v>9.3273394498177106E-2</v>
+        <v>0.33414232390613202</v>
       </c>
       <c r="K34" s="15">
-        <v>-1.86739517204689E-3</v>
+        <v>4.39836496781642E-3</v>
       </c>
       <c r="L34" s="16">
-        <v>-2.8236843902308601E-3</v>
+        <v>1.6809282215003799E-5</v>
       </c>
       <c r="M34" s="14">
-        <v>8.3022969830123892E-3</v>
+        <v>3.3564375225102398E-3</v>
       </c>
       <c r="N34" s="15">
-        <v>1.92274521616131E-2</v>
+        <v>1.92583699394182E-2</v>
       </c>
       <c r="O34" s="15">
-        <v>0.223611626935795</v>
+        <v>0.64189069914395902</v>
       </c>
       <c r="P34" s="15">
-        <v>-5.0965317621417903E-3</v>
+        <v>1.69707758124844E-3</v>
       </c>
       <c r="Q34" s="15">
-        <v>-2.7428830052050199E-2</v>
+        <v>0.100726239155483</v>
       </c>
       <c r="R34" s="15">
-        <v>1.9447800669093701E-3</v>
+        <v>9.2497168330190296E-2</v>
       </c>
       <c r="S34" s="16">
-        <v>-2.1623454921797299E-2</v>
+        <v>2.90525882570568E-2</v>
       </c>
     </row>
     <row r="35" spans="2:26">
@@ -16789,52 +20534,52 @@
         <v>10</v>
       </c>
       <c r="C35" s="9">
-        <v>0.13734565198507301</v>
+        <v>0</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="14">
-        <v>1.9889598950882802E-3</v>
+        <v>2.62192556255425E-5</v>
       </c>
       <c r="G35" s="15">
-        <v>4.2062850823392202E-3</v>
+        <v>6.3197232925129996E-6</v>
       </c>
       <c r="H35" s="15">
-        <v>-1.11642431611279E-3</v>
+        <v>3.3163913311739402E-5</v>
       </c>
       <c r="I35" s="15">
-        <v>-2.51516115049196E-2</v>
+        <v>2.6898544460889899E-5</v>
       </c>
       <c r="J35" s="15">
-        <v>-4.4794247516823198E-3</v>
+        <v>1.67021172807836E-3</v>
       </c>
       <c r="K35" s="15">
-        <v>9.8827456236635303E-2</v>
+        <v>0.35941429596570501</v>
       </c>
       <c r="L35" s="16">
-        <v>0.12446387549358801</v>
+        <v>0.545401670458598</v>
       </c>
       <c r="M35" s="14">
-        <v>5.5296339103878397E-3</v>
+        <v>2.06001186245117E-3</v>
       </c>
       <c r="N35" s="15">
-        <v>7.2267742091874799E-3</v>
+        <v>1.1340549495474899E-3</v>
       </c>
       <c r="O35" s="15">
-        <v>6.0280852769722297E-3</v>
+        <v>5.5996183039865501E-3</v>
       </c>
       <c r="P35" s="15">
-        <v>-4.4922728470797403E-2</v>
+        <v>1.01419117480234E-4</v>
       </c>
       <c r="Q35" s="15">
-        <v>-4.6717363066616597E-3</v>
+        <v>1.6087733278061099E-29</v>
       </c>
       <c r="R35" s="15">
-        <v>0.28647216251212898</v>
+        <v>0.56971283150864405</v>
       </c>
       <c r="S35" s="16">
-        <v>0.24249741720243601</v>
+        <v>0.37629260805942799</v>
       </c>
     </row>
     <row r="36" spans="2:26">
@@ -16842,52 +20587,52 @@
         <v>11</v>
       </c>
       <c r="C36" s="9">
-        <v>8.6727346929179203E-2</v>
+        <v>0</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F36" s="14">
-        <v>2.6970043490546401E-4</v>
+        <v>3.4770381222491801E-4</v>
       </c>
       <c r="G36" s="15">
-        <v>8.5631029315254899E-4</v>
+        <v>6.4540677342851501E-6</v>
       </c>
       <c r="H36" s="15">
-        <v>-4.6916488072681201E-4</v>
+        <v>4.9109290396500598E-4</v>
       </c>
       <c r="I36" s="15">
-        <v>2.1677143632677899E-2</v>
+        <v>5.8098068594065598E-2</v>
       </c>
       <c r="J36" s="15">
-        <v>1.4640814953949701E-2</v>
+        <v>0.11696243679262899</v>
       </c>
       <c r="K36" s="15">
-        <v>-1.4988455404217301E-4</v>
+        <v>1.63293461249832E-3</v>
       </c>
       <c r="L36" s="16">
-        <v>-2.8686260956249602E-3</v>
+        <v>7.23240649159251E-3</v>
       </c>
       <c r="M36" s="14">
-        <v>8.9549263289976299E-4</v>
+        <v>6.1963211372965195E-4</v>
       </c>
       <c r="N36" s="15">
-        <v>1.56846288612631E-3</v>
+        <v>2.0922456211876499E-3</v>
       </c>
       <c r="O36" s="15">
-        <v>1.2401404514744E-2</v>
+        <v>2.0329538581305401E-2</v>
       </c>
       <c r="P36" s="15">
-        <v>-5.5829974518071504E-4</v>
+        <v>2.55177758360834E-5</v>
       </c>
       <c r="Q36" s="15">
-        <v>5.5641820939758002E-3</v>
+        <v>2.28524910918467E-3</v>
       </c>
       <c r="R36" s="15">
-        <v>-4.6081047525570803E-4</v>
+        <v>3.3036468688813202E-4</v>
       </c>
       <c r="S36" s="16">
-        <v>-3.4115568056548601E-3</v>
+        <v>6.1655772501481804E-4</v>
       </c>
     </row>
     <row r="37" spans="2:26">
@@ -16895,52 +20640,52 @@
         <v>12</v>
       </c>
       <c r="C37" s="9">
-        <v>0.13193729779494401</v>
+        <v>0</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="14">
-        <v>-2.4502598103599702E-4</v>
+        <v>5.9602076280501105E-4</v>
       </c>
       <c r="G37" s="15">
-        <v>2.4127587815631099E-3</v>
+        <v>3.4053105158043E-5</v>
       </c>
       <c r="H37" s="15">
-        <v>-3.9310549530776798E-4</v>
+        <v>3.0394304532871798E-4</v>
       </c>
       <c r="I37" s="15">
-        <v>1.9063161470022901E-2</v>
+        <v>0.23498509377972601</v>
       </c>
       <c r="J37" s="15">
-        <v>1.44899973748453E-2</v>
+        <v>0.21921392911812901</v>
       </c>
       <c r="K37" s="15">
-        <v>-2.0375895958738501E-3</v>
+        <v>8.3704522765535802E-4</v>
       </c>
       <c r="L37" s="16">
-        <v>-3.3970123983393802E-3</v>
+        <v>2.5790085458784898E-4</v>
       </c>
       <c r="M37" s="14">
-        <v>1.8148492513055E-3</v>
+        <v>1.5773304443230901E-3</v>
       </c>
       <c r="N37" s="15">
-        <v>4.2567435888862803E-3</v>
+        <v>8.6090439885887302E-3</v>
       </c>
       <c r="O37" s="15">
-        <v>3.35070689951125E-2</v>
+        <v>3.8740350714422701E-2</v>
       </c>
       <c r="P37" s="15">
-        <v>-2.0081131500283601E-3</v>
+        <v>0.12389050748542001</v>
       </c>
       <c r="Q37" s="15">
-        <v>-2.93825814683394E-3</v>
+        <v>3.5548047006365898E-4</v>
       </c>
       <c r="R37" s="15">
-        <v>-1.3650191412132599E-3</v>
+        <v>8.1491721904260205E-4</v>
       </c>
       <c r="S37" s="16">
-        <v>-4.81753257590899E-3</v>
+        <v>2.1683236120082801E-4</v>
       </c>
     </row>
     <row r="38" spans="2:26">
@@ -16948,72 +20693,72 @@
         <v>13</v>
       </c>
       <c r="C38" s="10">
-        <v>3.3387290187160398E-2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="17">
-        <v>-5.4837373356472297E-4</v>
+        <v>4.4144504106273202E-46</v>
       </c>
       <c r="G38" s="18">
-        <v>2.31709402209819E-3</v>
+        <v>7.6016456007366099E-6</v>
       </c>
       <c r="H38" s="18">
-        <v>-9.6337620584894797E-4</v>
+        <v>2.15335989431515E-5</v>
       </c>
       <c r="I38" s="18">
-        <v>4.7859725651628701E-2</v>
+        <v>0.18350064159448301</v>
       </c>
       <c r="J38" s="18">
-        <v>1.2602050769776101E-2</v>
+        <v>0.15973841454718499</v>
       </c>
       <c r="K38" s="18">
-        <v>-4.48341518156283E-3</v>
+        <v>5.97391455725023E-4</v>
       </c>
       <c r="L38" s="19">
-        <v>6.6768650694746202E-3</v>
+        <v>4.7091487346916799E-4</v>
       </c>
       <c r="M38" s="17">
-        <v>4.26355182761704E-4</v>
+        <v>2.2807552400565801E-4</v>
       </c>
       <c r="N38" s="18">
-        <v>6.1308749749070298E-3</v>
+        <v>3.0099098874638002E-3</v>
       </c>
       <c r="O38" s="18">
-        <v>7.4836449183538498E-3</v>
+        <v>6.1912569811109E-3</v>
       </c>
       <c r="P38" s="18">
-        <v>-5.2673101410404704E-4</v>
+        <v>2.8970358336128502E-2</v>
       </c>
       <c r="Q38" s="18">
-        <v>-4.49498671140907E-3</v>
+        <v>7.6037839739496798E-4</v>
       </c>
       <c r="R38" s="18">
-        <v>-1.50001419227603E-3</v>
+        <v>2.1297811476091001E-4</v>
       </c>
       <c r="S38" s="19">
-        <v>-5.5762335056275397E-3</v>
+        <v>1.19828808286921E-3</v>
       </c>
     </row>
     <row r="41" spans="2:26">
-      <c r="E41" s="215" t="s">
+      <c r="E41" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="216"/>
-      <c r="G41" s="216"/>
-      <c r="H41" s="216"/>
-      <c r="I41" s="216"/>
-      <c r="J41" s="216"/>
-      <c r="K41" s="216"/>
-      <c r="L41" s="216"/>
-      <c r="M41" s="216"/>
-      <c r="N41" s="216"/>
-      <c r="O41" s="216"/>
-      <c r="P41" s="216"/>
-      <c r="Q41" s="216"/>
-      <c r="R41" s="216"/>
-      <c r="S41" s="217"/>
+      <c r="F41" s="228"/>
+      <c r="G41" s="228"/>
+      <c r="H41" s="228"/>
+      <c r="I41" s="228"/>
+      <c r="J41" s="228"/>
+      <c r="K41" s="228"/>
+      <c r="L41" s="228"/>
+      <c r="M41" s="228"/>
+      <c r="N41" s="228"/>
+      <c r="O41" s="228"/>
+      <c r="P41" s="228"/>
+      <c r="Q41" s="228"/>
+      <c r="R41" s="228"/>
+      <c r="S41" s="229"/>
     </row>
     <row r="43" spans="2:26">
       <c r="E43" s="40" t="s">
@@ -17792,23 +21537,23 @@
       </c>
     </row>
     <row r="59" spans="5:26">
-      <c r="E59" s="215" t="s">
+      <c r="E59" s="227" t="s">
         <v>34</v>
       </c>
-      <c r="F59" s="216"/>
-      <c r="G59" s="216"/>
-      <c r="H59" s="216"/>
-      <c r="I59" s="216"/>
-      <c r="J59" s="216"/>
-      <c r="K59" s="216"/>
-      <c r="L59" s="216"/>
-      <c r="M59" s="216"/>
-      <c r="N59" s="216"/>
-      <c r="O59" s="216"/>
-      <c r="P59" s="216"/>
-      <c r="Q59" s="216"/>
-      <c r="R59" s="216"/>
-      <c r="S59" s="217"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="228"/>
+      <c r="H59" s="228"/>
+      <c r="I59" s="228"/>
+      <c r="J59" s="228"/>
+      <c r="K59" s="228"/>
+      <c r="L59" s="228"/>
+      <c r="M59" s="228"/>
+      <c r="N59" s="228"/>
+      <c r="O59" s="228"/>
+      <c r="P59" s="228"/>
+      <c r="Q59" s="228"/>
+      <c r="R59" s="228"/>
+      <c r="S59" s="229"/>
     </row>
     <row r="61" spans="5:26">
       <c r="E61" s="40" t="s">
@@ -18664,23 +22409,23 @@
       </c>
     </row>
     <row r="77" spans="5:25">
-      <c r="E77" s="215" t="s">
+      <c r="E77" s="227" t="s">
         <v>35</v>
       </c>
-      <c r="F77" s="216"/>
-      <c r="G77" s="216"/>
-      <c r="H77" s="216"/>
-      <c r="I77" s="216"/>
-      <c r="J77" s="216"/>
-      <c r="K77" s="216"/>
-      <c r="L77" s="216"/>
-      <c r="M77" s="216"/>
-      <c r="N77" s="216"/>
-      <c r="O77" s="216"/>
-      <c r="P77" s="216"/>
-      <c r="Q77" s="216"/>
-      <c r="R77" s="216"/>
-      <c r="S77" s="217"/>
+      <c r="F77" s="228"/>
+      <c r="G77" s="228"/>
+      <c r="H77" s="228"/>
+      <c r="I77" s="228"/>
+      <c r="J77" s="228"/>
+      <c r="K77" s="228"/>
+      <c r="L77" s="228"/>
+      <c r="M77" s="228"/>
+      <c r="N77" s="228"/>
+      <c r="O77" s="228"/>
+      <c r="P77" s="228"/>
+      <c r="Q77" s="228"/>
+      <c r="R77" s="228"/>
+      <c r="S77" s="229"/>
       <c r="V77" s="54">
         <f>Y77/V$3</f>
         <v>13.825195195195196</v>
@@ -19399,23 +23144,23 @@
       </c>
     </row>
     <row r="95" spans="5:19">
-      <c r="E95" s="215" t="s">
+      <c r="E95" s="227" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="216"/>
-      <c r="G95" s="216"/>
-      <c r="H95" s="216"/>
-      <c r="I95" s="216"/>
-      <c r="J95" s="216"/>
-      <c r="K95" s="216"/>
-      <c r="L95" s="216"/>
-      <c r="M95" s="216"/>
-      <c r="N95" s="216"/>
-      <c r="O95" s="216"/>
-      <c r="P95" s="216"/>
-      <c r="Q95" s="216"/>
-      <c r="R95" s="216"/>
-      <c r="S95" s="217"/>
+      <c r="F95" s="228"/>
+      <c r="G95" s="228"/>
+      <c r="H95" s="228"/>
+      <c r="I95" s="228"/>
+      <c r="J95" s="228"/>
+      <c r="K95" s="228"/>
+      <c r="L95" s="228"/>
+      <c r="M95" s="228"/>
+      <c r="N95" s="228"/>
+      <c r="O95" s="228"/>
+      <c r="P95" s="228"/>
+      <c r="Q95" s="228"/>
+      <c r="R95" s="228"/>
+      <c r="S95" s="229"/>
     </row>
     <row r="97" spans="5:19">
       <c r="E97" s="40" t="s">
@@ -20190,8 +23935,8 @@
       <c r="O115" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P115" s="218"/>
-      <c r="Q115" s="218"/>
+      <c r="P115" s="215"/>
+      <c r="Q115" s="215"/>
       <c r="R115" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20259,10 +24004,10 @@
       <c r="H117" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I117" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J117" s="218"/>
+      <c r="I117" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J117" s="215"/>
       <c r="K117" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20278,10 +24023,10 @@
       <c r="O117" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P117" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q117" s="218"/>
+      <c r="P117" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q117" s="215"/>
       <c r="R117" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20302,12 +24047,12 @@
       <c r="H118" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I118" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J118" s="218"/>
-      <c r="K118" s="218"/>
-      <c r="L118" s="219"/>
+      <c r="I118" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J118" s="215"/>
+      <c r="K118" s="215"/>
+      <c r="L118" s="216"/>
       <c r="M118" s="32">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20323,8 +24068,8 @@
       <c r="Q118" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R118" s="218"/>
-      <c r="S118" s="219"/>
+      <c r="R118" s="215"/>
+      <c r="S118" s="216"/>
     </row>
     <row r="119" spans="5:19">
       <c r="E119" s="45" t="s">
@@ -20339,14 +24084,14 @@
       <c r="H119" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I119" s="218">
+      <c r="I119" s="215">
         <v>2.0799999999999999E-4</v>
       </c>
-      <c r="J119" s="218"/>
-      <c r="K119" s="218">
+      <c r="J119" s="215"/>
+      <c r="K119" s="215">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L119" s="219"/>
+      <c r="L119" s="216"/>
       <c r="M119" s="32">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20362,8 +24107,8 @@
       <c r="Q119" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R119" s="218"/>
-      <c r="S119" s="219"/>
+      <c r="R119" s="215"/>
+      <c r="S119" s="216"/>
     </row>
     <row r="120" spans="5:19">
       <c r="E120" s="46" t="s">
@@ -20378,17 +24123,17 @@
       <c r="H120" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I120" s="220"/>
-      <c r="J120" s="220">
+      <c r="I120" s="217"/>
+      <c r="J120" s="217">
         <v>1.098E-3</v>
       </c>
-      <c r="K120" s="220">
+      <c r="K120" s="217">
         <v>0.17</v>
       </c>
-      <c r="L120" s="221">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="M120" s="227"/>
+      <c r="L120" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M120" s="224"/>
       <c r="N120" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20401,8 +24146,8 @@
       <c r="Q120" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R120" s="220"/>
-      <c r="S120" s="221"/>
+      <c r="R120" s="217"/>
+      <c r="S120" s="218"/>
     </row>
     <row r="121" spans="5:19">
       <c r="E121" s="44" t="s">
@@ -20464,8 +24209,8 @@
       <c r="H122" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I122" s="222"/>
-      <c r="J122" s="222"/>
+      <c r="I122" s="219"/>
+      <c r="J122" s="219"/>
       <c r="K122" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20554,10 +24299,10 @@
       <c r="H124" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I124" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J124" s="222"/>
+      <c r="I124" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J124" s="219"/>
       <c r="K124" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20573,10 +24318,10 @@
       <c r="O124" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P124" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q124" s="222"/>
+      <c r="P124" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q124" s="219"/>
       <c r="R124" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20603,8 +24348,8 @@
       <c r="J125" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K125" s="222"/>
-      <c r="L125" s="224"/>
+      <c r="K125" s="219"/>
+      <c r="L125" s="221"/>
       <c r="M125" s="14">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20614,14 +24359,14 @@
       <c r="O125" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P125" s="222">
+      <c r="P125" s="219">
         <v>7.6029999999999998</v>
       </c>
-      <c r="Q125" s="222"/>
-      <c r="R125" s="222">
+      <c r="Q125" s="219"/>
+      <c r="R125" s="219">
         <v>3.0699999999999998E-4</v>
       </c>
-      <c r="S125" s="224">
+      <c r="S125" s="221">
         <v>1E-3</v>
       </c>
     </row>
@@ -20644,10 +24389,10 @@
       <c r="J126" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K126" s="222">
+      <c r="K126" s="219">
         <v>1.04E-2</v>
       </c>
-      <c r="L126" s="224">
+      <c r="L126" s="221">
         <v>1.98E-3</v>
       </c>
       <c r="M126" s="14">
@@ -20659,20 +24404,20 @@
       <c r="O126" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P126" s="222">
+      <c r="P126" s="219">
         <v>9.8200000000000002E-4</v>
       </c>
-      <c r="Q126" s="222"/>
-      <c r="R126" s="222">
+      <c r="Q126" s="219"/>
+      <c r="R126" s="219">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="S126" s="224"/>
+      <c r="S126" s="221"/>
     </row>
     <row r="127" spans="5:19">
       <c r="E127" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F127" s="226"/>
+      <c r="F127" s="223"/>
       <c r="G127" s="18">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20685,8 +24430,8 @@
       <c r="J127" s="18">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="K127" s="223"/>
-      <c r="L127" s="225">
+      <c r="K127" s="220"/>
+      <c r="L127" s="222">
         <v>1.02</v>
       </c>
       <c r="M127" s="17">
@@ -20698,14 +24443,14 @@
       <c r="O127" s="18">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P127" s="223">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q127" s="223"/>
-      <c r="R127" s="223">
+      <c r="P127" s="220">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q127" s="220"/>
+      <c r="R127" s="220">
         <v>1.168E-3</v>
       </c>
-      <c r="S127" s="225"/>
+      <c r="S127" s="222"/>
     </row>
     <row r="129" spans="5:19">
       <c r="E129" s="40" t="s">
@@ -20835,8 +24580,8 @@
       <c r="O131" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P131" s="218"/>
-      <c r="Q131" s="218"/>
+      <c r="P131" s="215"/>
+      <c r="Q131" s="215"/>
       <c r="R131" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20904,10 +24649,10 @@
       <c r="H133" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I133" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J133" s="218"/>
+      <c r="I133" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J133" s="215"/>
       <c r="K133" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20923,10 +24668,10 @@
       <c r="O133" s="30">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="P133" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q133" s="218"/>
+      <c r="P133" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q133" s="215"/>
       <c r="R133" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20947,12 +24692,12 @@
       <c r="H134" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I134" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J134" s="218"/>
-      <c r="K134" s="218"/>
-      <c r="L134" s="219"/>
+      <c r="I134" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J134" s="215"/>
+      <c r="K134" s="215"/>
+      <c r="L134" s="216"/>
       <c r="M134" s="32">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -20968,8 +24713,8 @@
       <c r="Q134" s="30">
         <v>9.7499999999999996E-4</v>
       </c>
-      <c r="R134" s="218"/>
-      <c r="S134" s="219"/>
+      <c r="R134" s="215"/>
+      <c r="S134" s="216"/>
     </row>
     <row r="135" spans="5:19">
       <c r="E135" s="45" t="s">
@@ -20984,14 +24729,14 @@
       <c r="H135" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I135" s="218">
+      <c r="I135" s="215">
         <v>6.0399999999999896E-4</v>
       </c>
-      <c r="J135" s="218"/>
-      <c r="K135" s="218">
+      <c r="J135" s="215"/>
+      <c r="K135" s="215">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L135" s="219"/>
+      <c r="L135" s="216"/>
       <c r="M135" s="32">
         <v>1.99E-3</v>
       </c>
@@ -21007,8 +24752,8 @@
       <c r="Q135" s="30">
         <v>1E-3</v>
       </c>
-      <c r="R135" s="218"/>
-      <c r="S135" s="219"/>
+      <c r="R135" s="215"/>
+      <c r="S135" s="216"/>
     </row>
     <row r="136" spans="5:19">
       <c r="E136" s="46" t="s">
@@ -21023,17 +24768,17 @@
       <c r="H136" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I136" s="220"/>
-      <c r="J136" s="220">
+      <c r="I136" s="217"/>
+      <c r="J136" s="217">
         <v>1.294E-3</v>
       </c>
-      <c r="K136" s="220">
+      <c r="K136" s="217">
         <v>0.17</v>
       </c>
-      <c r="L136" s="221">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="M136" s="227"/>
+      <c r="L136" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M136" s="224"/>
       <c r="N136" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21046,8 +24791,8 @@
       <c r="Q136" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="R136" s="220"/>
-      <c r="S136" s="221"/>
+      <c r="R136" s="217"/>
+      <c r="S136" s="218"/>
     </row>
     <row r="137" spans="5:19">
       <c r="E137" s="44" t="s">
@@ -21109,8 +24854,8 @@
       <c r="H138" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I138" s="222"/>
-      <c r="J138" s="222"/>
+      <c r="I138" s="219"/>
+      <c r="J138" s="219"/>
       <c r="K138" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21199,10 +24944,10 @@
       <c r="H140" s="15">
         <v>7.59699999999999E-3</v>
       </c>
-      <c r="I140" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J140" s="222"/>
+      <c r="I140" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J140" s="219"/>
       <c r="K140" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21218,10 +24963,10 @@
       <c r="O140" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P140" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q140" s="222"/>
+      <c r="P140" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q140" s="219"/>
       <c r="R140" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21248,8 +24993,8 @@
       <c r="J141" s="15">
         <v>9.8400000000000007E-4</v>
       </c>
-      <c r="K141" s="222"/>
-      <c r="L141" s="224"/>
+      <c r="K141" s="219"/>
+      <c r="L141" s="221"/>
       <c r="M141" s="14">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21259,14 +25004,14 @@
       <c r="O141" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P141" s="222">
+      <c r="P141" s="219">
         <v>7.6029999999999998</v>
       </c>
-      <c r="Q141" s="222"/>
-      <c r="R141" s="222">
+      <c r="Q141" s="219"/>
+      <c r="R141" s="219">
         <v>9.01E-4</v>
       </c>
-      <c r="S141" s="224">
+      <c r="S141" s="221">
         <v>1E-3</v>
       </c>
     </row>
@@ -21289,10 +25034,10 @@
       <c r="J142" s="15">
         <v>9.9500000000000001E-4</v>
       </c>
-      <c r="K142" s="222">
+      <c r="K142" s="219">
         <v>2.91999999999999E-2</v>
       </c>
-      <c r="L142" s="224">
+      <c r="L142" s="221">
         <v>1.98E-3</v>
       </c>
       <c r="M142" s="14">
@@ -21304,20 +25049,20 @@
       <c r="O142" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P142" s="222">
+      <c r="P142" s="219">
         <v>9.859999999999999E-4</v>
       </c>
-      <c r="Q142" s="222"/>
-      <c r="R142" s="222">
+      <c r="Q142" s="219"/>
+      <c r="R142" s="219">
         <v>1.5999999999999901E-3</v>
       </c>
-      <c r="S142" s="224"/>
+      <c r="S142" s="221"/>
     </row>
     <row r="143" spans="5:19">
       <c r="E143" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F143" s="226"/>
+      <c r="F143" s="223"/>
       <c r="G143" s="18">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21330,8 +25075,8 @@
       <c r="J143" s="18">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="K143" s="223"/>
-      <c r="L143" s="225">
+      <c r="K143" s="220"/>
+      <c r="L143" s="222">
         <v>1.02</v>
       </c>
       <c r="M143" s="17">
@@ -21343,14 +25088,14 @@
       <c r="O143" s="18">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="P143" s="223">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q143" s="223"/>
-      <c r="R143" s="223">
+      <c r="P143" s="220">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q143" s="220"/>
+      <c r="R143" s="220">
         <v>1.5839999999999999E-3</v>
       </c>
-      <c r="S143" s="225"/>
+      <c r="S143" s="222"/>
     </row>
     <row r="145" spans="5:19">
       <c r="E145" s="40" t="s">
@@ -21480,8 +25225,8 @@
       <c r="O147" s="30">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="P147" s="218"/>
-      <c r="Q147" s="218"/>
+      <c r="P147" s="215"/>
+      <c r="Q147" s="215"/>
       <c r="R147" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21549,10 +25294,10 @@
       <c r="H149" s="30">
         <v>1E-3</v>
       </c>
-      <c r="I149" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J149" s="218"/>
+      <c r="I149" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J149" s="215"/>
       <c r="K149" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21568,10 +25313,10 @@
       <c r="O149" s="30">
         <v>2E-3</v>
       </c>
-      <c r="P149" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q149" s="218"/>
+      <c r="P149" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q149" s="215"/>
       <c r="R149" s="30">
         <v>9.8499999999999998E-4</v>
       </c>
@@ -21592,12 +25337,12 @@
       <c r="H150" s="30">
         <v>9.6000000000000002E-4</v>
       </c>
-      <c r="I150" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J150" s="218"/>
-      <c r="K150" s="218"/>
-      <c r="L150" s="219"/>
+      <c r="I150" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J150" s="215"/>
+      <c r="K150" s="215"/>
+      <c r="L150" s="216"/>
       <c r="M150" s="32">
         <v>9.8999999999999999E-4</v>
       </c>
@@ -21613,8 +25358,8 @@
       <c r="Q150" s="30">
         <v>1E-3</v>
       </c>
-      <c r="R150" s="218"/>
-      <c r="S150" s="219"/>
+      <c r="R150" s="215"/>
+      <c r="S150" s="216"/>
     </row>
     <row r="151" spans="5:19">
       <c r="E151" s="45" t="s">
@@ -21629,14 +25374,14 @@
       <c r="H151" s="30">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="I151" s="218">
+      <c r="I151" s="215">
         <v>1E-3</v>
       </c>
-      <c r="J151" s="218"/>
-      <c r="K151" s="218">
+      <c r="J151" s="215"/>
+      <c r="K151" s="215">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L151" s="219"/>
+      <c r="L151" s="216"/>
       <c r="M151" s="32">
         <v>9.9950000000000004E-3</v>
       </c>
@@ -21652,8 +25397,8 @@
       <c r="Q151" s="30">
         <v>1E-3</v>
       </c>
-      <c r="R151" s="218"/>
-      <c r="S151" s="219"/>
+      <c r="R151" s="215"/>
+      <c r="S151" s="216"/>
     </row>
     <row r="152" spans="5:19">
       <c r="E152" s="46" t="s">
@@ -21668,17 +25413,17 @@
       <c r="H152" s="36">
         <v>9.7999999999999997E-4</v>
       </c>
-      <c r="I152" s="220"/>
-      <c r="J152" s="220">
+      <c r="I152" s="217"/>
+      <c r="J152" s="217">
         <v>1.49E-3</v>
       </c>
-      <c r="K152" s="220">
+      <c r="K152" s="217">
         <v>0.17</v>
       </c>
-      <c r="L152" s="221">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="M152" s="227"/>
+      <c r="L152" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M152" s="224"/>
       <c r="N152" s="36">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21691,8 +25436,8 @@
       <c r="Q152" s="36">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="R152" s="220"/>
-      <c r="S152" s="221"/>
+      <c r="R152" s="217"/>
+      <c r="S152" s="218"/>
     </row>
     <row r="153" spans="5:19">
       <c r="E153" s="44" t="s">
@@ -21754,8 +25499,8 @@
       <c r="H154" s="15">
         <v>1E-3</v>
       </c>
-      <c r="I154" s="222"/>
-      <c r="J154" s="222"/>
+      <c r="I154" s="219"/>
+      <c r="J154" s="219"/>
       <c r="K154" s="15">
         <v>9.2000000000000003E-4</v>
       </c>
@@ -21844,10 +25589,10 @@
       <c r="H156" s="15">
         <v>4.5499999999999999E-2</v>
       </c>
-      <c r="I156" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J156" s="222"/>
+      <c r="I156" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J156" s="219"/>
       <c r="K156" s="15">
         <v>9.7499999999999996E-4</v>
       </c>
@@ -21863,10 +25608,10 @@
       <c r="O156" s="15">
         <v>1E-3</v>
       </c>
-      <c r="P156" s="222">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q156" s="222"/>
+      <c r="P156" s="219">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q156" s="219"/>
       <c r="R156" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -21893,8 +25638,8 @@
       <c r="J157" s="15">
         <v>1E-3</v>
       </c>
-      <c r="K157" s="222"/>
-      <c r="L157" s="224"/>
+      <c r="K157" s="219"/>
+      <c r="L157" s="221"/>
       <c r="M157" s="14">
         <v>9.7000000000000005E-4</v>
       </c>
@@ -21904,14 +25649,14 @@
       <c r="O157" s="15">
         <v>9.3999999999999997E-4</v>
       </c>
-      <c r="P157" s="222">
+      <c r="P157" s="219">
         <v>7.6029999999999998</v>
       </c>
-      <c r="Q157" s="222"/>
-      <c r="R157" s="222">
+      <c r="Q157" s="219"/>
+      <c r="R157" s="219">
         <v>0.01</v>
       </c>
-      <c r="S157" s="224">
+      <c r="S157" s="221">
         <v>1E-3</v>
       </c>
     </row>
@@ -21934,10 +25679,10 @@
       <c r="J158" s="15">
         <v>1E-3</v>
       </c>
-      <c r="K158" s="222">
+      <c r="K158" s="219">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="L158" s="224">
+      <c r="L158" s="221">
         <v>1.98E-3</v>
       </c>
       <c r="M158" s="14">
@@ -21949,20 +25694,20 @@
       <c r="O158" s="15">
         <v>9.3000000000000005E-4</v>
       </c>
-      <c r="P158" s="222">
+      <c r="P158" s="219">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="Q158" s="222"/>
-      <c r="R158" s="222">
+      <c r="Q158" s="219"/>
+      <c r="R158" s="219">
         <v>2E-3</v>
       </c>
-      <c r="S158" s="224"/>
+      <c r="S158" s="221"/>
     </row>
     <row r="159" spans="5:19">
       <c r="E159" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F159" s="226"/>
+      <c r="F159" s="223"/>
       <c r="G159" s="18">
         <v>9.6500000000000004E-4</v>
       </c>
@@ -21975,8 +25720,8 @@
       <c r="J159" s="18">
         <v>1E-3</v>
       </c>
-      <c r="K159" s="223"/>
-      <c r="L159" s="225">
+      <c r="K159" s="220"/>
+      <c r="L159" s="222">
         <v>1.02</v>
       </c>
       <c r="M159" s="17">
@@ -21988,14 +25733,14 @@
       <c r="O159" s="18">
         <v>9.7000000000000005E-4</v>
       </c>
-      <c r="P159" s="223">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q159" s="223"/>
-      <c r="R159" s="223">
+      <c r="P159" s="220">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q159" s="220"/>
+      <c r="R159" s="220">
         <v>2E-3</v>
       </c>
-      <c r="S159" s="225"/>
+      <c r="S159" s="222"/>
     </row>
     <row r="161" spans="5:19">
       <c r="E161" s="40" t="s">
@@ -22125,8 +25870,8 @@
       <c r="O163" s="30">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="P163" s="218"/>
-      <c r="Q163" s="218"/>
+      <c r="P163" s="215"/>
+      <c r="Q163" s="215"/>
       <c r="R163" s="30">
         <v>9.8099999999999902E-4</v>
       </c>
@@ -22194,10 +25939,10 @@
       <c r="H165" s="30">
         <v>1E-3</v>
       </c>
-      <c r="I165" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J165" s="218"/>
+      <c r="I165" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J165" s="215"/>
       <c r="K165" s="30">
         <v>9.6000000000000002E-4</v>
       </c>
@@ -22213,10 +25958,10 @@
       <c r="O165" s="30">
         <v>1.6199999999999899E-2</v>
       </c>
-      <c r="P165" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q165" s="218"/>
+      <c r="P165" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q165" s="215"/>
       <c r="R165" s="30">
         <v>1E-3</v>
       </c>
@@ -22237,12 +25982,12 @@
       <c r="H166" s="30">
         <v>1E-3</v>
       </c>
-      <c r="I166" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J166" s="218"/>
-      <c r="K166" s="218"/>
-      <c r="L166" s="219"/>
+      <c r="I166" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J166" s="215"/>
+      <c r="K166" s="215"/>
+      <c r="L166" s="216"/>
       <c r="M166" s="32">
         <v>4.10929999999999E-2</v>
       </c>
@@ -22258,8 +26003,8 @@
       <c r="Q166" s="30">
         <v>1E-3</v>
       </c>
-      <c r="R166" s="218"/>
-      <c r="S166" s="219"/>
+      <c r="R166" s="215"/>
+      <c r="S166" s="216"/>
     </row>
     <row r="167" spans="5:19">
       <c r="E167" s="45" t="s">
@@ -22274,14 +26019,14 @@
       <c r="H167" s="30">
         <v>1E-3</v>
       </c>
-      <c r="I167" s="218">
+      <c r="I167" s="215">
         <v>3.9789999999999899</v>
       </c>
-      <c r="J167" s="218"/>
-      <c r="K167" s="218">
+      <c r="J167" s="215"/>
+      <c r="K167" s="215">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L167" s="219"/>
+      <c r="L167" s="216"/>
       <c r="M167" s="32">
         <v>8.4385999999999906E-2</v>
       </c>
@@ -22297,8 +26042,8 @@
       <c r="Q167" s="30">
         <v>1.9859999999999999E-3</v>
       </c>
-      <c r="R167" s="218"/>
-      <c r="S167" s="219"/>
+      <c r="R167" s="215"/>
+      <c r="S167" s="216"/>
     </row>
     <row r="168" spans="5:19">
       <c r="E168" s="46" t="s">
@@ -22313,17 +26058,17 @@
       <c r="H168" s="36">
         <v>1E-3</v>
       </c>
-      <c r="I168" s="220"/>
-      <c r="J168" s="220">
+      <c r="I168" s="217"/>
+      <c r="J168" s="217">
         <v>1.686E-3</v>
       </c>
-      <c r="K168" s="220">
+      <c r="K168" s="217">
         <v>0.17</v>
       </c>
-      <c r="L168" s="221">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="M168" s="227"/>
+      <c r="L168" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M168" s="224"/>
       <c r="N168" s="36">
         <v>9.8999999999999999E-4</v>
       </c>
@@ -22336,8 +26081,8 @@
       <c r="Q168" s="36">
         <v>1E-3</v>
       </c>
-      <c r="R168" s="220"/>
-      <c r="S168" s="221"/>
+      <c r="R168" s="217"/>
+      <c r="S168" s="218"/>
     </row>
     <row r="169" spans="5:19">
       <c r="E169" s="44" t="s">
@@ -22399,8 +26144,8 @@
       <c r="H170" s="15">
         <v>8.3099999999999896E-2</v>
       </c>
-      <c r="I170" s="222"/>
-      <c r="J170" s="222"/>
+      <c r="I170" s="219"/>
+      <c r="J170" s="219"/>
       <c r="K170" s="15">
         <v>1E-3</v>
       </c>
@@ -22489,10 +26234,10 @@
       <c r="H172" s="15">
         <v>8.1699999999999898E-2</v>
       </c>
-      <c r="I172" s="222">
+      <c r="I172" s="219">
         <v>0.33090899999999801</v>
       </c>
-      <c r="J172" s="222"/>
+      <c r="J172" s="219"/>
       <c r="K172" s="15">
         <v>1E-3</v>
       </c>
@@ -22508,10 +26253,10 @@
       <c r="O172" s="15">
         <v>1E-3</v>
       </c>
-      <c r="P172" s="222">
+      <c r="P172" s="219">
         <v>1.08999999999999E-4</v>
       </c>
-      <c r="Q172" s="222"/>
+      <c r="Q172" s="219"/>
       <c r="R172" s="15">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -22538,8 +26283,8 @@
       <c r="J173" s="15">
         <v>1E-3</v>
       </c>
-      <c r="K173" s="222"/>
-      <c r="L173" s="224"/>
+      <c r="K173" s="219"/>
+      <c r="L173" s="221"/>
       <c r="M173" s="14">
         <v>1.98E-3</v>
       </c>
@@ -22549,14 +26294,14 @@
       <c r="O173" s="15">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="P173" s="222">
+      <c r="P173" s="219">
         <v>7.6029999999999998</v>
       </c>
-      <c r="Q173" s="222"/>
-      <c r="R173" s="222">
+      <c r="Q173" s="219"/>
+      <c r="R173" s="219">
         <v>3.7799999999999903E-2</v>
       </c>
-      <c r="S173" s="224">
+      <c r="S173" s="221">
         <v>1E-3</v>
       </c>
     </row>
@@ -22579,10 +26324,10 @@
       <c r="J174" s="15">
         <v>1E-3</v>
       </c>
-      <c r="K174" s="222">
+      <c r="K174" s="219">
         <v>6.6799999999999901E-2</v>
       </c>
-      <c r="L174" s="224">
+      <c r="L174" s="221">
         <v>1.98E-3</v>
       </c>
       <c r="M174" s="14">
@@ -22594,20 +26339,20 @@
       <c r="O174" s="15">
         <v>9.8999999999999999E-4</v>
       </c>
-      <c r="P174" s="222">
+      <c r="P174" s="219">
         <v>2.8593999999999901E-2</v>
       </c>
-      <c r="Q174" s="222"/>
-      <c r="R174" s="222">
+      <c r="Q174" s="219"/>
+      <c r="R174" s="219">
         <v>5.1999999999999998E-3</v>
       </c>
-      <c r="S174" s="224"/>
+      <c r="S174" s="221"/>
     </row>
     <row r="175" spans="5:19">
       <c r="E175" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F175" s="226"/>
+      <c r="F175" s="223"/>
       <c r="G175" s="18">
         <v>9.8999999999999999E-4</v>
       </c>
@@ -22620,8 +26365,8 @@
       <c r="J175" s="18">
         <v>1E-3</v>
       </c>
-      <c r="K175" s="223"/>
-      <c r="L175" s="225">
+      <c r="K175" s="220"/>
+      <c r="L175" s="222">
         <v>1.02</v>
       </c>
       <c r="M175" s="17">
@@ -22633,14 +26378,14 @@
       <c r="O175" s="18">
         <v>1E-3</v>
       </c>
-      <c r="P175" s="223">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q175" s="223"/>
-      <c r="R175" s="223">
+      <c r="P175" s="220">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q175" s="220"/>
+      <c r="R175" s="220">
         <v>2.3999999999999998E-3</v>
       </c>
-      <c r="S175" s="225"/>
+      <c r="S175" s="222"/>
     </row>
     <row r="177" spans="5:19">
       <c r="E177" s="40" t="s">
@@ -22770,8 +26515,8 @@
       <c r="O179" s="30">
         <v>0.35830000000000001</v>
       </c>
-      <c r="P179" s="218"/>
-      <c r="Q179" s="218"/>
+      <c r="P179" s="215"/>
+      <c r="Q179" s="215"/>
       <c r="R179" s="30">
         <v>1E-3</v>
       </c>
@@ -22839,10 +26584,10 @@
       <c r="H181" s="30">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="I181" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J181" s="218"/>
+      <c r="I181" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J181" s="215"/>
       <c r="K181" s="30">
         <v>1E-3</v>
       </c>
@@ -22858,10 +26603,10 @@
       <c r="O181" s="30">
         <v>0.13439400000000001</v>
       </c>
-      <c r="P181" s="218">
+      <c r="P181" s="215">
         <v>5.9800000000000001E-4</v>
       </c>
-      <c r="Q181" s="218"/>
+      <c r="Q181" s="215"/>
       <c r="R181" s="30">
         <v>2E-3</v>
       </c>
@@ -22882,12 +26627,12 @@
       <c r="H182" s="30">
         <v>2E-3</v>
       </c>
-      <c r="I182" s="218">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="J182" s="218"/>
-      <c r="K182" s="218"/>
-      <c r="L182" s="219"/>
+      <c r="I182" s="215">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="J182" s="215"/>
+      <c r="K182" s="215"/>
+      <c r="L182" s="216"/>
       <c r="M182" s="32">
         <v>0.26679999999999898</v>
       </c>
@@ -22903,8 +26648,8 @@
       <c r="Q182" s="30">
         <v>2E-3</v>
       </c>
-      <c r="R182" s="218"/>
-      <c r="S182" s="219"/>
+      <c r="R182" s="215"/>
+      <c r="S182" s="216"/>
     </row>
     <row r="183" spans="5:19">
       <c r="E183" s="45" t="s">
@@ -22919,14 +26664,14 @@
       <c r="H183" s="30">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="I183" s="218">
+      <c r="I183" s="215">
         <v>7.9569999999999999</v>
       </c>
-      <c r="J183" s="218"/>
-      <c r="K183" s="218">
+      <c r="J183" s="215"/>
+      <c r="K183" s="215">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="L183" s="219"/>
+      <c r="L183" s="216"/>
       <c r="M183" s="32">
         <v>0.30790000000000001</v>
       </c>
@@ -22942,8 +26687,8 @@
       <c r="Q183" s="30">
         <v>2E-3</v>
       </c>
-      <c r="R183" s="218"/>
-      <c r="S183" s="219"/>
+      <c r="R183" s="215"/>
+      <c r="S183" s="216"/>
     </row>
     <row r="184" spans="5:19">
       <c r="E184" s="46" t="s">
@@ -22958,17 +26703,17 @@
       <c r="H184" s="36">
         <v>2E-3</v>
       </c>
-      <c r="I184" s="220"/>
-      <c r="J184" s="220">
+      <c r="I184" s="217"/>
+      <c r="J184" s="217">
         <v>1.882E-3</v>
       </c>
-      <c r="K184" s="220">
+      <c r="K184" s="217">
         <v>0.17</v>
       </c>
-      <c r="L184" s="221">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="M184" s="227"/>
+      <c r="L184" s="218">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="M184" s="224"/>
       <c r="N184" s="36">
         <v>1.99E-3</v>
       </c>
@@ -22981,8 +26726,8 @@
       <c r="Q184" s="36">
         <v>2E-3</v>
       </c>
-      <c r="R184" s="220"/>
-      <c r="S184" s="221"/>
+      <c r="R184" s="217"/>
+      <c r="S184" s="218"/>
     </row>
     <row r="185" spans="5:19">
       <c r="E185" s="44" t="s">
@@ -23044,8 +26789,8 @@
       <c r="H186" s="15">
         <v>0.42170000000000002</v>
       </c>
-      <c r="I186" s="222"/>
-      <c r="J186" s="222"/>
+      <c r="I186" s="219"/>
+      <c r="J186" s="219"/>
       <c r="K186" s="15">
         <v>1E-3</v>
       </c>
@@ -23134,10 +26879,10 @@
       <c r="H188" s="15">
         <v>0.28710000000000002</v>
       </c>
-      <c r="I188" s="222">
+      <c r="I188" s="219">
         <v>2.316303</v>
       </c>
-      <c r="J188" s="222"/>
+      <c r="J188" s="219"/>
       <c r="K188" s="15">
         <v>2E-3</v>
       </c>
@@ -23153,10 +26898,10 @@
       <c r="O188" s="15">
         <v>1.0699999999999999E-2</v>
       </c>
-      <c r="P188" s="222">
+      <c r="P188" s="219">
         <v>7.0299999999999996E-4</v>
       </c>
-      <c r="Q188" s="222"/>
+      <c r="Q188" s="219"/>
       <c r="R188" s="15">
         <v>1E-3</v>
       </c>
@@ -23183,8 +26928,8 @@
       <c r="J189" s="15">
         <v>2E-3</v>
       </c>
-      <c r="K189" s="222"/>
-      <c r="L189" s="224"/>
+      <c r="K189" s="219"/>
+      <c r="L189" s="221"/>
       <c r="M189" s="14">
         <v>0.16020000000000001</v>
       </c>
@@ -23194,14 +26939,14 @@
       <c r="O189" s="15">
         <v>2E-3</v>
       </c>
-      <c r="P189" s="222">
+      <c r="P189" s="219">
         <v>7.6029999999999998</v>
       </c>
-      <c r="Q189" s="222"/>
-      <c r="R189" s="222">
+      <c r="Q189" s="219"/>
+      <c r="R189" s="219">
         <v>0.15060000000000001</v>
       </c>
-      <c r="S189" s="224">
+      <c r="S189" s="221">
         <v>1E-3</v>
       </c>
     </row>
@@ -23224,10 +26969,10 @@
       <c r="J190" s="15">
         <v>2E-3</v>
       </c>
-      <c r="K190" s="222">
+      <c r="K190" s="219">
         <v>8.5599999999999996E-2</v>
       </c>
-      <c r="L190" s="224">
+      <c r="L190" s="221">
         <v>1.98E-3</v>
       </c>
       <c r="M190" s="14">
@@ -23239,20 +26984,20 @@
       <c r="O190" s="15">
         <v>2.9839999999999901E-3</v>
       </c>
-      <c r="P190" s="222">
+      <c r="P190" s="219">
         <v>5.6197999999999998E-2</v>
       </c>
-      <c r="Q190" s="222"/>
-      <c r="R190" s="222">
+      <c r="Q190" s="219"/>
+      <c r="R190" s="219">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="S190" s="224"/>
+      <c r="S190" s="221"/>
     </row>
     <row r="191" spans="5:19">
       <c r="E191" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="F191" s="226"/>
+      <c r="F191" s="223"/>
       <c r="G191" s="18">
         <v>2E-3</v>
       </c>
@@ -23265,8 +27010,8 @@
       <c r="J191" s="18">
         <v>2E-3</v>
       </c>
-      <c r="K191" s="223"/>
-      <c r="L191" s="225">
+      <c r="K191" s="220"/>
+      <c r="L191" s="222">
         <v>1.02</v>
       </c>
       <c r="M191" s="17">
@@ -23278,33 +27023,33 @@
       <c r="O191" s="18">
         <v>1.98E-3</v>
       </c>
-      <c r="P191" s="223">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="Q191" s="223"/>
-      <c r="R191" s="223">
+      <c r="P191" s="220">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="Q191" s="220"/>
+      <c r="R191" s="220">
         <v>2.8E-3</v>
       </c>
-      <c r="S191" s="225"/>
+      <c r="S191" s="222"/>
     </row>
     <row r="193" spans="5:19">
-      <c r="E193" s="215" t="s">
+      <c r="E193" s="227" t="s">
         <v>38</v>
       </c>
-      <c r="F193" s="216"/>
-      <c r="G193" s="216"/>
-      <c r="H193" s="216"/>
-      <c r="I193" s="216"/>
-      <c r="J193" s="216"/>
-      <c r="K193" s="216"/>
-      <c r="L193" s="216"/>
-      <c r="M193" s="216"/>
-      <c r="N193" s="216"/>
-      <c r="O193" s="216"/>
-      <c r="P193" s="216"/>
-      <c r="Q193" s="216"/>
-      <c r="R193" s="216"/>
-      <c r="S193" s="217"/>
+      <c r="F193" s="228"/>
+      <c r="G193" s="228"/>
+      <c r="H193" s="228"/>
+      <c r="I193" s="228"/>
+      <c r="J193" s="228"/>
+      <c r="K193" s="228"/>
+      <c r="L193" s="228"/>
+      <c r="M193" s="228"/>
+      <c r="N193" s="228"/>
+      <c r="O193" s="228"/>
+      <c r="P193" s="228"/>
+      <c r="Q193" s="228"/>
+      <c r="R193" s="228"/>
+      <c r="S193" s="229"/>
     </row>
     <row r="195" spans="5:19">
       <c r="E195" s="40" t="s">
